--- a/data/artifacts/daily_median_metrics.xlsx
+++ b/data/artifacts/daily_median_metrics.xlsx
@@ -1,37 +1,375 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>median_real_power_w</t>
+  </si>
+  <si>
+    <t>median_direct_wm2</t>
+  </si>
+  <si>
+    <t>median_diffuse_wm2</t>
+  </si>
+  <si>
+    <t>median_temp_k</t>
+  </si>
+  <si>
+    <t>physical_nMAE</t>
+  </si>
+  <si>
+    <t>physical_nRMSE</t>
+  </si>
+  <si>
+    <t>physical_count</t>
+  </si>
+  <si>
+    <t>source_nMAE</t>
+  </si>
+  <si>
+    <t>source_nRMSE</t>
+  </si>
+  <si>
+    <t>source_count</t>
+  </si>
+  <si>
+    <t>target_nMAE</t>
+  </si>
+  <si>
+    <t>target_nRMSE</t>
+  </si>
+  <si>
+    <t>target_count</t>
+  </si>
+  <si>
+    <t>transfer_nMAE</t>
+  </si>
+  <si>
+    <t>transfer_nRMSE</t>
+  </si>
+  <si>
+    <t>transfer_count</t>
+  </si>
+  <si>
+    <t>2025-07-07</t>
+  </si>
+  <si>
+    <t>2025-07-08</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>2025-07-10</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>2025-07-12</t>
+  </si>
+  <si>
+    <t>2025-07-13</t>
+  </si>
+  <si>
+    <t>2025-07-14</t>
+  </si>
+  <si>
+    <t>2025-07-15</t>
+  </si>
+  <si>
+    <t>2025-07-16</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>2025-07-18</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>2025-07-21</t>
+  </si>
+  <si>
+    <t>2025-07-22</t>
+  </si>
+  <si>
+    <t>2025-07-23</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>2025-07-25</t>
+  </si>
+  <si>
+    <t>2025-07-26</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>2025-07-29</t>
+  </si>
+  <si>
+    <t>2025-07-30</t>
+  </si>
+  <si>
+    <t>2025-07-31</t>
+  </si>
+  <si>
+    <t>2025-08-01</t>
+  </si>
+  <si>
+    <t>2025-08-02</t>
+  </si>
+  <si>
+    <t>2025-08-03</t>
+  </si>
+  <si>
+    <t>2025-08-04</t>
+  </si>
+  <si>
+    <t>2025-08-05</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>2025-08-07</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>2025-08-09</t>
+  </si>
+  <si>
+    <t>2025-08-10</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>2025-08-12</t>
+  </si>
+  <si>
+    <t>2025-08-13</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>2025-08-15</t>
+  </si>
+  <si>
+    <t>2025-08-16</t>
+  </si>
+  <si>
+    <t>2025-08-17</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>2025-08-19</t>
+  </si>
+  <si>
+    <t>2025-08-20</t>
+  </si>
+  <si>
+    <t>2025-08-21</t>
+  </si>
+  <si>
+    <t>2025-08-22</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>2025-08-24</t>
+  </si>
+  <si>
+    <t>2025-08-25</t>
+  </si>
+  <si>
+    <t>2025-08-26</t>
+  </si>
+  <si>
+    <t>2025-08-27</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>2025-08-29</t>
+  </si>
+  <si>
+    <t>2025-08-30</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>2025-09-01</t>
+  </si>
+  <si>
+    <t>2025-09-02</t>
+  </si>
+  <si>
+    <t>2025-09-03</t>
+  </si>
+  <si>
+    <t>2025-09-04</t>
+  </si>
+  <si>
+    <t>2025-09-05</t>
+  </si>
+  <si>
+    <t>2025-09-06</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>2025-09-08</t>
+  </si>
+  <si>
+    <t>2025-09-09</t>
+  </si>
+  <si>
+    <t>2025-09-10</t>
+  </si>
+  <si>
+    <t>2025-09-11</t>
+  </si>
+  <si>
+    <t>2025-09-12</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>2025-09-14</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>2025-09-16</t>
+  </si>
+  <si>
+    <t>2025-09-17</t>
+  </si>
+  <si>
+    <t>2025-09-18</t>
+  </si>
+  <si>
+    <t>2025-09-19</t>
+  </si>
+  <si>
+    <t>2025-09-20</t>
+  </si>
+  <si>
+    <t>2025-09-21</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>2025-09-23</t>
+  </si>
+  <si>
+    <t>2025-09-24</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>2025-09-27</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>2025-09-29</t>
+  </si>
+  <si>
+    <t>2025-09-30</t>
+  </si>
+  <si>
+    <t>2025-10-01</t>
+  </si>
+  <si>
+    <t>2025-10-02</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>2025-10-05</t>
+  </si>
+  <si>
+    <t>2025-10-06</t>
+  </si>
+  <si>
+    <t>2025-10-07</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +384,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,5217 +700,4993 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q94"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>median_real_power_w</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>median_direct_wm2</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>median_diffuse_wm2</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>median_temp_k</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>physical_nMAE</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>physical_nRMSE</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>physical_count</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>source_nMAE</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>source_nRMSE</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>source_count</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>target_nMAE</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>target_nRMSE</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>target_count</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>transfer_nMAE</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>transfer_nRMSE</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>transfer_count</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:17">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
         <v>926.4799999999988</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>32.26566699999967</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>157.5736699999998</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>289.2341156005859</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>0.10225482037542</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>0.1498433657997423</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>891</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>0.0851689244296729</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>0.1205900188098535</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>214</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>0.1373641506813084</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>0.1747191712291752</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>214</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2">
         <v>0.1165132139144859</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2">
         <v>0.1438024526463331</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2">
         <v>214</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2025-07-08</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:17">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
         <v>1629.759666666666</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>28.375</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>148.1801859999996</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>287.6587219238281</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>0.0898961643310454</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>0.1291588230946339</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>891</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>0.0869562169045997</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>0.1210361178232596</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>662</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>0.1227481825148338</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>0.1531950127527595</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3">
         <v>662</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3">
         <v>0.07966376288845919</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3">
         <v>0.0999315798732494</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3">
         <v>662</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:17">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
         <v>1446.647333333331</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>79.15156999999817</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>177.7742500000004</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>287.8675994873047</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>0.1041985424548223</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>0.1403562972681628</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>877</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>0.08925658454331011</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>0.1168706164483048</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>877</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>0.0914768171278221</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>0.1209303435765521</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4">
         <v>877</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4">
         <v>0.0845485324935233</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4">
         <v>0.1073039320753317</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4">
         <v>877</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:17">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5">
         <v>2065.604666666665</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>113.7110309999998</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>178.5856899999999</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>289.5373840332031</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>0.09897949958786501</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>0.1371787360711638</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>877</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>0.09130304572712419</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>0.1203402351720561</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>877</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>0.08734439629754839</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>0.1123604919251179</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5">
         <v>877</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5">
         <v>0.1042143113295895</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5">
         <v>0.1335474951650214</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5">
         <v>877</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:17">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6">
         <v>2482.638999999998</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>120.6323499999999</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>175.9838780000009</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>290.9632263183594</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>0.1062245043688298</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>0.1486755533242489</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>877</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>0.1329911057821778</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>0.1640031944095697</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>877</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>0.1088413711925883</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>0.1334170676958813</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6">
         <v>877</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6">
         <v>0.1133523660405017</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6">
         <v>0.1364133711939033</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6">
         <v>877</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:17">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7">
         <v>2427.204333333332</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>86.82812000000013</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>179.2341899999992</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>291.2043151855469</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>0.0932160926293548</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>0.1327176133016057</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>877</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>0.1192047259455028</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>0.1520080946414183</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>877</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>0.0901812493654002</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>0.1203306588299509</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7">
         <v>877</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7">
         <v>0.0931083364192702</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7">
         <v>0.1184599637198136</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7">
         <v>877</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2025-07-13</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:17">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8">
         <v>3383.692333333331</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>353.671875</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>105.8426599999998</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>292.9872970581055</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>0.0825608077072385</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>0.1013196301072755</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>877</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>0.1236635000501984</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>0.1508556461764241</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>877</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>0.084747429704789</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>0.110225239092753</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8">
         <v>877</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8">
         <v>0.08934163224064991</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8">
         <v>0.1113118997754076</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8">
         <v>877</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2025-07-14</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:17">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9">
         <v>1333.467999999997</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>28.16389999999956</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>167.0425940000005</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>292.7091217041016</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>0.1014763741285132</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>0.1392467358789182</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>863</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>0.1102833204389571</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>0.1518345059615729</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>863</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>0.1045305937282996</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>0.1376131482333943</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9">
         <v>863</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9">
         <v>0.1063553572213905</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9">
         <v>0.1354837285712498</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9">
         <v>863</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:17">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10">
         <v>1157.012999999998</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>47.1293958</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>165.1885099999981</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>291.7108154296875</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>0.1353236428336299</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>0.1807441415438043</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>863</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>0.1110517145735631</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>0.1527374169762866</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>863</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>0.0821272321454692</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>0.1149966033334028</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10">
         <v>863</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10">
         <v>0.0925422303780996</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10">
         <v>0.1205431002515849</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10">
         <v>863</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2025-07-16</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:17">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11">
         <v>1426.324666666665</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>10.28018599999905</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>141.2609400000001</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>289.7492904663086</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>0.0920933892829997</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>0.1345971662809172</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>863</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>0.082545029636358</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>0.1221520745122105</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>863</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>0.0831977181028041</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>0.1060158965957792</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11">
         <v>863</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11">
         <v>0.0731311462176245</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11">
         <v>0.0949022399059231</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11">
         <v>863</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2025-07-17</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:17">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12">
         <v>1652.473333333333</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>120.59375</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>176.4486300000008</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>289.3332214355469</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>0.1100614567995553</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>0.1448499903072626</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>863</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>0.1410097903578099</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>0.1768482818953783</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>863</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>0.0967209624933951</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>0.1301257255036227</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12">
         <v>863</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O12">
         <v>0.09478464843580529</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P12">
         <v>0.1234712731311515</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q12">
         <v>863</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2025-07-18</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:17">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13">
         <v>3178.633666666666</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>210.23387</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>135.0993900000012</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>291.0202713012696</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>0.0895100948600985</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>0.1081124567359332</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>863</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>0.1333260180427867</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>0.1594960504941753</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>863</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>0.0600358185173661</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13">
         <v>0.0815950117745808</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13">
         <v>863</v>
       </c>
-      <c r="O13" t="n">
+      <c r="O13">
         <v>0.07019128487740441</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P13">
         <v>0.0897074928112086</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q13">
         <v>863</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2025-07-19</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:17">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14">
         <v>3208.491</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>352.6751799999984</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>110.7247100000004</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>294.1616668701172</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>0.09975924161787859</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>0.1232088632019755</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>863</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>0.1309157810524449</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>0.1658923744706107</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>863</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>0.0508587684155272</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14">
         <v>0.06558800066539409</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14">
         <v>863</v>
       </c>
-      <c r="O14" t="n">
+      <c r="O14">
         <v>0.0612342278705677</v>
       </c>
-      <c r="P14" t="n">
+      <c r="P14">
         <v>0.07645124362209969</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q14">
         <v>863</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:17">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15">
         <v>3441.936333333333</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>261.9160299999999</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>136.05099</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>292.4948272705078</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>0.0780940495666546</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>0.0943876077816844</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>863</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>0.1013997253656964</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>0.1273927148985618</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>863</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>0.0593867263756894</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15">
         <v>0.07504656947294371</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15">
         <v>863</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O15">
         <v>0.0670335740602433</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P15">
         <v>0.08606834330587181</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q15">
         <v>863</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2025-07-21</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+    <row r="16" spans="1:17">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16">
         <v>671.2000000000002</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>1.935120999999981</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>105.272574999999</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>291.5233459472656</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>0.0624784388553335</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>0.1002170140401514</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>863</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>0.1235682288900115</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>0.1665723028446444</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>863</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>0.1372288933737311</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16">
         <v>0.1675161413994616</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16">
         <v>863</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O16">
         <v>0.1138909668910428</v>
       </c>
-      <c r="P16" t="n">
+      <c r="P16">
         <v>0.1402421479213391</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q16">
         <v>863</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
+    <row r="17" spans="1:17">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17">
         <v>1729.4085</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>33.01577999999972</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>154.2188800000022</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>290.4378967285156</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>0.0984106115650101</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>0.1316824421995095</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>863</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>0.1162796538500231</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>0.1520047213025715</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17">
         <v>863</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17">
         <v>0.07680201545129781</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17">
         <v>0.1047291979818672</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17">
         <v>863</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O17">
         <v>0.07464070466681801</v>
       </c>
-      <c r="P17" t="n">
+      <c r="P17">
         <v>0.1005270815172983</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q17">
         <v>863</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
+    <row r="18" spans="1:17">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18">
         <v>3563.978333333333</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>319.3085300000002</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>119.4102599999969</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>290.9064025878906</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>0.07099177102967651</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18">
         <v>0.0881368762911684</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18">
         <v>863</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18">
         <v>0.1199931935011703</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18">
         <v>0.1531859597949807</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18">
         <v>863</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18">
         <v>0.08339093376433369</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18">
         <v>0.1073162587172877</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18">
         <v>863</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O18">
         <v>0.09326916755434531</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P18">
         <v>0.1154514974565125</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q18">
         <v>863</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
+    <row r="19" spans="1:17">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19">
         <v>700.6653333333337</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>5.21875</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>131.88688</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>290.0395050048828</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>0.1105193234681285</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19">
         <v>0.1600240665058054</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19">
         <v>863</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19">
         <v>0.1205159450993916</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19">
         <v>0.1761307854349799</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19">
         <v>863</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19">
         <v>0.1222162737222085</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19">
         <v>0.1513288329285743</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19">
         <v>863</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O19">
         <v>0.1166063768201483</v>
       </c>
-      <c r="P19" t="n">
+      <c r="P19">
         <v>0.1437625159165305</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="Q19">
         <v>863</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
+    <row r="20" spans="1:17">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20">
         <v>1839.565666666668</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>9.49246699999958</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>172.7216200000003</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>289.6408538818359</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>0.08013251803582171</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20">
         <v>0.1147571569039358</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20">
         <v>849</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20">
         <v>0.0953749394469493</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20">
         <v>0.1278151193065741</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20">
         <v>849</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20">
         <v>0.0623948461362073</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20">
         <v>0.0935828256617133</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20">
         <v>849</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O20">
         <v>0.0662338295570318</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P20">
         <v>0.0952545571854105</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q20">
         <v>849</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
+    <row r="21" spans="1:17">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21">
         <v>651.1306666666682</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>1.7578125</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>137.1248600000008</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>289.8584442138672</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>0.0885789991558075</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21">
         <v>0.1305259838705156</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21">
         <v>849</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21">
         <v>0.1004622958352768</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21">
         <v>0.1510769309808874</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21">
         <v>849</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21">
         <v>0.0862978417801884</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21">
         <v>0.102519829766062</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21">
         <v>849</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O21">
         <v>0.092324810459305</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P21">
         <v>0.1103555200815985</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q21">
         <v>849</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2025-07-27</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
+    <row r="22" spans="1:17">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22">
         <v>1263.973666666668</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>58.0390625</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>174.4917200000018</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>289.2681579589844</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>0.1268989067652089</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22">
         <v>0.1765573984283554</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22">
         <v>835</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22">
         <v>0.12763091815497</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22">
         <v>0.1678702984186441</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22">
         <v>835</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22">
         <v>0.09051451736772451</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22">
         <v>0.1213162346649173</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22">
         <v>835</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O22">
         <v>0.0966360506445509</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P22">
         <v>0.1237099199962646</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q22">
         <v>835</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
+    <row r="23" spans="1:17">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23">
         <v>944.9076666666678</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>1.090970000000198</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>106.1367539999999</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>288.0597534179688</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>0.0487423946806813</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23">
         <v>0.0728380652653965</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23">
         <v>835</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23">
         <v>0.0708572423349652</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23">
         <v>0.0907782029833735</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23">
         <v>835</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23">
         <v>0.0601810219770658</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M23">
         <v>0.07334634477917271</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N23">
         <v>835</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O23">
         <v>0.06349969312104189</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P23">
         <v>0.0781431301416507</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q23">
         <v>835</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
+    <row r="24" spans="1:17">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24">
         <v>1737.030666666668</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>98.42290400000002</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>165.372416000002</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>288.0841293334961</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>0.1126867857908387</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24">
         <v>0.1434745891664447</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24">
         <v>835</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24">
         <v>0.1107449171013652</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24">
         <v>0.1425501135383978</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K24">
         <v>835</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24">
         <v>0.0885683552710778</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M24">
         <v>0.1209895504143769</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N24">
         <v>835</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O24">
         <v>0.08041233950376039</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P24">
         <v>0.1040300482474789</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q24">
         <v>835</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
+    <row r="25" spans="1:17">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25">
         <v>1366.584666666667</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>19.29889000000003</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>177.4168499999996</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>288.3186798095703</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>0.0868375413202854</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25">
         <v>0.1160342049556428</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25">
         <v>835</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25">
         <v>0.08936085172065859</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J25">
         <v>0.1167282676267492</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K25">
         <v>835</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L25">
         <v>0.0612460721597185</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M25">
         <v>0.0763203672382677</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N25">
         <v>835</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O25">
         <v>0.0539548643426347</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P25">
         <v>0.0704772504167996</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q25">
         <v>835</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
+    <row r="26" spans="1:17">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26">
         <v>1752.544333333333</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>44.22431299999971</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>161.8450800000028</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>289.1337432861328</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>0.0981771480801443</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26">
         <v>0.1270091175382583</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26">
         <v>835</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26">
         <v>0.09919016498420349</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J26">
         <v>0.1218964170125071</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K26">
         <v>835</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L26">
         <v>0.0941731305765149</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M26">
         <v>0.1262106645080395</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N26">
         <v>835</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O26">
         <v>0.0803657390968503</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P26">
         <v>0.1035263524911343</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q26">
         <v>835</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
+    <row r="27" spans="1:17">
+      <c r="A27" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27">
         <v>1277.609</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>23.06077499999992</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>152.0274499999996</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>289.3163452148437</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27">
         <v>0.1207312044713071</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27">
         <v>0.167884824242556</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27">
         <v>835</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27">
         <v>0.1320919189081437</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J27">
         <v>0.1685923910839543</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K27">
         <v>835</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L27">
         <v>0.1138722014654012</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M27">
         <v>0.1459828552264917</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N27">
         <v>835</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O27">
         <v>0.1151581889190898</v>
       </c>
-      <c r="P27" t="n">
+      <c r="P27">
         <v>0.1437802043307078</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="Q27">
         <v>835</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
+    <row r="28" spans="1:17">
+      <c r="A28" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28">
         <v>790.5469999999997</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>2.234375</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>120.1120900000005</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28">
         <v>288.1733093261719</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28">
         <v>0.0729586560981804</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28">
         <v>0.1091793597088852</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28">
         <v>835</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28">
         <v>0.0785532518561281</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J28">
         <v>0.112406286311535</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K28">
         <v>835</v>
       </c>
-      <c r="L28" t="n">
+      <c r="L28">
         <v>0.0486018565062754</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M28">
         <v>0.0641019956048728</v>
       </c>
-      <c r="N28" t="n">
+      <c r="N28">
         <v>835</v>
       </c>
-      <c r="O28" t="n">
+      <c r="O28">
         <v>0.0551906301246706</v>
       </c>
-      <c r="P28" t="n">
+      <c r="P28">
         <v>0.0724508283715912</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="Q28">
         <v>835</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
+    <row r="29" spans="1:17">
+      <c r="A29" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29">
         <v>1449.673</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>31.28125140000003</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>143.1792800000003</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29">
         <v>287.0264282226562</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29">
         <v>0.1040209381094081</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29">
         <v>0.1406499791686715</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29">
         <v>835</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29">
         <v>0.09256631904998799</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J29">
         <v>0.1233747072998824</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K29">
         <v>835</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L29">
         <v>0.0718574201010431</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M29">
         <v>0.0986064300229503</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N29">
         <v>835</v>
       </c>
-      <c r="O29" t="n">
+      <c r="O29">
         <v>0.073253729656982</v>
       </c>
-      <c r="P29" t="n">
+      <c r="P29">
         <v>0.0997860902772426</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="Q29">
         <v>835</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
+    <row r="30" spans="1:17">
+      <c r="A30" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30">
         <v>753.64</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>1.274319000000105</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>91.33777499999997</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30">
         <v>288.3782501220703</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30">
         <v>0.0529748752204373</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30">
         <v>0.0807159049421519</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30">
         <v>835</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30">
         <v>0.0643874378195281</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J30">
         <v>0.0862382830401146</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K30">
         <v>835</v>
       </c>
-      <c r="L30" t="n">
+      <c r="L30">
         <v>0.0839687847161317</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M30">
         <v>0.1030323034420964</v>
       </c>
-      <c r="N30" t="n">
+      <c r="N30">
         <v>835</v>
       </c>
-      <c r="O30" t="n">
+      <c r="O30">
         <v>0.0582460402428742</v>
       </c>
-      <c r="P30" t="n">
+      <c r="P30">
         <v>0.0757747275442486</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="Q30">
         <v>835</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
+    <row r="31" spans="1:17">
+      <c r="A31" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31">
         <v>2040.162</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>111.1720499999992</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>160.1168400000006</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31">
         <v>288.8148651123047</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31">
         <v>0.0987270827439479</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31">
         <v>0.1350700708506771</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31">
         <v>821</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31">
         <v>0.1219834475258343</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J31">
         <v>0.1667878996617113</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K31">
         <v>821</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L31">
         <v>0.0951978223350182</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M31">
         <v>0.1193758664383373</v>
       </c>
-      <c r="N31" t="n">
+      <c r="N31">
         <v>821</v>
       </c>
-      <c r="O31" t="n">
+      <c r="O31">
         <v>0.0868213141438855</v>
       </c>
-      <c r="P31" t="n">
+      <c r="P31">
         <v>0.1123770071220242</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="Q31">
         <v>821</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
+    <row r="32" spans="1:17">
+      <c r="A32" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32">
         <v>3577.863333333334</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>322.3494949999986</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32">
         <v>138.0329699999998</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32">
         <v>289.7502136230469</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32">
         <v>0.0862946942958781</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G32">
         <v>0.09404215997136479</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32">
         <v>821</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I32">
         <v>0.1408873711061388</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J32">
         <v>0.1694474451696912</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K32">
         <v>821</v>
       </c>
-      <c r="L32" t="n">
+      <c r="L32">
         <v>0.0689754035197807</v>
       </c>
-      <c r="M32" t="n">
+      <c r="M32">
         <v>0.0880560358646129</v>
       </c>
-      <c r="N32" t="n">
+      <c r="N32">
         <v>821</v>
       </c>
-      <c r="O32" t="n">
+      <c r="O32">
         <v>0.0580378604391473</v>
       </c>
-      <c r="P32" t="n">
+      <c r="P32">
         <v>0.07323359737280299</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q32">
         <v>821</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
+    <row r="33" spans="1:17">
+      <c r="A33" t="s">
+        <v>48</v>
+      </c>
+      <c r="B33">
         <v>3524.414000000001</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>398.2671399999981</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>110.8926400000009</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33">
         <v>291.172119140625</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33">
         <v>0.08822804582428451</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G33">
         <v>0.098095349499378</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H33">
         <v>821</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I33">
         <v>0.1421117366099634</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J33">
         <v>0.1802518378059374</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K33">
         <v>821</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L33">
         <v>0.064388329604933</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M33">
         <v>0.0832953253376149</v>
       </c>
-      <c r="N33" t="n">
+      <c r="N33">
         <v>821</v>
       </c>
-      <c r="O33" t="n">
+      <c r="O33">
         <v>0.0535047097942265</v>
       </c>
-      <c r="P33" t="n">
+      <c r="P33">
         <v>0.06625874568088699</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="Q33">
         <v>821</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
+    <row r="34" spans="1:17">
+      <c r="A34" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34">
         <v>3153.808000000001</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>403.3477300000004</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>101.0139199999994</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34">
         <v>294.1332855224609</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34">
         <v>0.0970645714649423</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G34">
         <v>0.1065355241119329</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H34">
         <v>807</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I34">
         <v>0.1519133060887484</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J34">
         <v>0.194852964671184</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K34">
         <v>807</v>
       </c>
-      <c r="L34" t="n">
+      <c r="L34">
         <v>0.0459832498835935</v>
       </c>
-      <c r="M34" t="n">
+      <c r="M34">
         <v>0.0596695241028679</v>
       </c>
-      <c r="N34" t="n">
+      <c r="N34">
         <v>807</v>
       </c>
-      <c r="O34" t="n">
+      <c r="O34">
         <v>0.0534785688883519</v>
       </c>
-      <c r="P34" t="n">
+      <c r="P34">
         <v>0.07028642462363389</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="Q34">
         <v>807</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
+    <row r="35" spans="1:17">
+      <c r="A35" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35">
         <v>3388.682333333335</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>399.5045</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35">
         <v>106.3989600000004</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35">
         <v>296.2169342041016</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35">
         <v>0.09208850855174509</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G35">
         <v>0.1012305880730822</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H35">
         <v>807</v>
       </c>
-      <c r="I35" t="n">
+      <c r="I35">
         <v>0.1563767957060718</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J35">
         <v>0.197264402231974</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K35">
         <v>807</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L35">
         <v>0.0366315697908215</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M35">
         <v>0.046241175494995</v>
       </c>
-      <c r="N35" t="n">
+      <c r="N35">
         <v>807</v>
       </c>
-      <c r="O35" t="n">
+      <c r="O35">
         <v>0.0514149013372986</v>
       </c>
-      <c r="P35" t="n">
+      <c r="P35">
         <v>0.0640839548529967</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="Q35">
         <v>807</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
+    <row r="36" spans="1:17">
+      <c r="A36" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36">
         <v>3410.697333333334</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>373.1333799999993</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>109.9371999999994</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36">
         <v>295.0440063476562</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36">
         <v>0.08823944852787639</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G36">
         <v>0.0968374904124852</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H36">
         <v>807</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I36">
         <v>0.1380759846752106</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J36">
         <v>0.1768541107330134</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K36">
         <v>807</v>
       </c>
-      <c r="L36" t="n">
+      <c r="L36">
         <v>0.031361064374907</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M36">
         <v>0.0386477087559251</v>
       </c>
-      <c r="N36" t="n">
+      <c r="N36">
         <v>807</v>
       </c>
-      <c r="O36" t="n">
+      <c r="O36">
         <v>0.0423900406571251</v>
       </c>
-      <c r="P36" t="n">
+      <c r="P36">
         <v>0.0533643447885289</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="Q36">
         <v>807</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
+    <row r="37" spans="1:17">
+      <c r="A37" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37">
         <v>3471.077333333334</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37">
         <v>419.6744199999994</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37">
         <v>102.568718</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37">
         <v>293.2339935302734</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37">
         <v>0.0935387215950058</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G37">
         <v>0.1019748876035122</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H37">
         <v>807</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I37">
         <v>0.1550417003775712</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J37">
         <v>0.1985318354531243</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K37">
         <v>807</v>
       </c>
-      <c r="L37" t="n">
+      <c r="L37">
         <v>0.0257345414632173</v>
       </c>
-      <c r="M37" t="n">
+      <c r="M37">
         <v>0.0326544114892648</v>
       </c>
-      <c r="N37" t="n">
+      <c r="N37">
         <v>807</v>
       </c>
-      <c r="O37" t="n">
+      <c r="O37">
         <v>0.043387168340793</v>
       </c>
-      <c r="P37" t="n">
+      <c r="P37">
         <v>0.0553541973437196</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="Q37">
         <v>807</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
+    <row r="38" spans="1:17">
+      <c r="A38" t="s">
+        <v>53</v>
+      </c>
+      <c r="B38">
         <v>3373.021000000001</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38">
         <v>409.5464399999983</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38">
         <v>102.8899199999996</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38">
         <v>294.5586471557617</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38">
         <v>0.09572979627045471</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G38">
         <v>0.1053694764776509</v>
       </c>
-      <c r="H38" t="n">
+      <c r="H38">
         <v>807</v>
       </c>
-      <c r="I38" t="n">
+      <c r="I38">
         <v>0.1556729873186121</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J38">
         <v>0.1994998954458122</v>
       </c>
-      <c r="K38" t="n">
+      <c r="K38">
         <v>807</v>
       </c>
-      <c r="L38" t="n">
+      <c r="L38">
         <v>0.0250463620998389</v>
       </c>
-      <c r="M38" t="n">
+      <c r="M38">
         <v>0.0311660185451333</v>
       </c>
-      <c r="N38" t="n">
+      <c r="N38">
         <v>807</v>
       </c>
-      <c r="O38" t="n">
+      <c r="O38">
         <v>0.0432937477119083</v>
       </c>
-      <c r="P38" t="n">
+      <c r="P38">
         <v>0.0541636342468674</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="Q38">
         <v>807</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
+    <row r="39" spans="1:17">
+      <c r="A39" t="s">
+        <v>54</v>
+      </c>
+      <c r="B39">
         <v>3314.572666666667</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39">
         <v>422.4050399999978</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39">
         <v>96.58616000000076</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39">
         <v>297.50048828125</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39">
         <v>0.0965900697997636</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G39">
         <v>0.1055545682153933</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H39">
         <v>807</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I39">
         <v>0.1569035062619455</v>
       </c>
-      <c r="J39" t="n">
+      <c r="J39">
         <v>0.1970108523903772</v>
       </c>
-      <c r="K39" t="n">
+      <c r="K39">
         <v>807</v>
       </c>
-      <c r="L39" t="n">
+      <c r="L39">
         <v>0.0221661551389715</v>
       </c>
-      <c r="M39" t="n">
+      <c r="M39">
         <v>0.0273399050198559</v>
       </c>
-      <c r="N39" t="n">
+      <c r="N39">
         <v>807</v>
       </c>
-      <c r="O39" t="n">
+      <c r="O39">
         <v>0.039981597761425</v>
       </c>
-      <c r="P39" t="n">
+      <c r="P39">
         <v>0.0506027935300075</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="Q39">
         <v>807</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
+    <row r="40" spans="1:17">
+      <c r="A40" t="s">
+        <v>55</v>
+      </c>
+      <c r="B40">
         <v>3056.276000000001</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40">
         <v>355.3827800000072</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40">
         <v>109.5815980000007</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40">
         <v>298.8911590576172</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40">
         <v>0.1001857142675864</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G40">
         <v>0.115847064235145</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H40">
         <v>793</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I40">
         <v>0.1443472804525687</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J40">
         <v>0.1746209150263873</v>
       </c>
-      <c r="K40" t="n">
+      <c r="K40">
         <v>793</v>
       </c>
-      <c r="L40" t="n">
+      <c r="L40">
         <v>0.0308030192608701</v>
       </c>
-      <c r="M40" t="n">
+      <c r="M40">
         <v>0.0467887555123254</v>
       </c>
-      <c r="N40" t="n">
+      <c r="N40">
         <v>793</v>
       </c>
-      <c r="O40" t="n">
+      <c r="O40">
         <v>0.0429493040043757</v>
       </c>
-      <c r="P40" t="n">
+      <c r="P40">
         <v>0.056777795404849</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="Q40">
         <v>793</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
+    <row r="41" spans="1:17">
+      <c r="A41" t="s">
+        <v>56</v>
+      </c>
+      <c r="B41">
         <v>2935.750333333334</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41">
         <v>301.2381399999995</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41">
         <v>109.9691679999996</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41">
         <v>296.2611083984375</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41">
         <v>0.0903166380533436</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G41">
         <v>0.1169190792473684</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H41">
         <v>793</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I41">
         <v>0.1196933125178436</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J41">
         <v>0.1485221782465175</v>
       </c>
-      <c r="K41" t="n">
+      <c r="K41">
         <v>793</v>
       </c>
-      <c r="L41" t="n">
+      <c r="L41">
         <v>0.0504528567604413</v>
       </c>
-      <c r="M41" t="n">
+      <c r="M41">
         <v>0.0676026468148495</v>
       </c>
-      <c r="N41" t="n">
+      <c r="N41">
         <v>793</v>
       </c>
-      <c r="O41" t="n">
+      <c r="O41">
         <v>0.0554609411619167</v>
       </c>
-      <c r="P41" t="n">
+      <c r="P41">
         <v>0.0721092485356804</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="Q41">
         <v>793</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
+    <row r="42" spans="1:17">
+      <c r="A42" t="s">
+        <v>57</v>
+      </c>
+      <c r="B42">
         <v>583.3606666666672</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42">
         <v>55.71486100000004</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42">
         <v>185.9909699999998</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42">
         <v>294.9087829589844</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42">
         <v>0.162141200208837</v>
       </c>
-      <c r="G42" t="n">
+      <c r="G42">
         <v>0.2031419048808702</v>
       </c>
-      <c r="H42" t="n">
+      <c r="H42">
         <v>793</v>
       </c>
-      <c r="I42" t="n">
+      <c r="I42">
         <v>0.1773107195862597</v>
       </c>
-      <c r="J42" t="n">
+      <c r="J42">
         <v>0.2379712942511535</v>
       </c>
-      <c r="K42" t="n">
+      <c r="K42">
         <v>793</v>
       </c>
-      <c r="L42" t="n">
+      <c r="L42">
         <v>0.1334059959083215</v>
       </c>
-      <c r="M42" t="n">
+      <c r="M42">
         <v>0.158137867069121</v>
       </c>
-      <c r="N42" t="n">
+      <c r="N42">
         <v>793</v>
       </c>
-      <c r="O42" t="n">
+      <c r="O42">
         <v>0.1292243761508196</v>
       </c>
-      <c r="P42" t="n">
+      <c r="P42">
         <v>0.155730698348541</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="Q42">
         <v>793</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
+    <row r="43" spans="1:17">
+      <c r="A43" t="s">
+        <v>58</v>
+      </c>
+      <c r="B43">
         <v>1848.209333333333</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43">
         <v>203.2881360000001</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43">
         <v>160.7939200000019</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43">
         <v>291.8735427856445</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43">
         <v>0.1108583324171915</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G43">
         <v>0.1470076362509573</v>
       </c>
-      <c r="H43" t="n">
+      <c r="H43">
         <v>793</v>
       </c>
-      <c r="I43" t="n">
+      <c r="I43">
         <v>0.1439285736131904</v>
       </c>
-      <c r="J43" t="n">
+      <c r="J43">
         <v>0.1819769607095201</v>
       </c>
-      <c r="K43" t="n">
+      <c r="K43">
         <v>793</v>
       </c>
-      <c r="L43" t="n">
+      <c r="L43">
         <v>0.07593619369343001</v>
       </c>
-      <c r="M43" t="n">
+      <c r="M43">
         <v>0.0973494861362913</v>
       </c>
-      <c r="N43" t="n">
+      <c r="N43">
         <v>793</v>
       </c>
-      <c r="O43" t="n">
+      <c r="O43">
         <v>0.07489062708305801</v>
       </c>
-      <c r="P43" t="n">
+      <c r="P43">
         <v>0.097594752278946</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="Q43">
         <v>793</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
+    <row r="44" spans="1:17">
+      <c r="A44" t="s">
+        <v>59</v>
+      </c>
+      <c r="B44">
         <v>3045.403333333334</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44">
         <v>388.2935960000013</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44">
         <v>105.5637070000002</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44">
         <v>290.8590087890625</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44">
         <v>0.1008291329036761</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G44">
         <v>0.11131383865014</v>
       </c>
-      <c r="H44" t="n">
+      <c r="H44">
         <v>793</v>
       </c>
-      <c r="I44" t="n">
+      <c r="I44">
         <v>0.1549692601453972</v>
       </c>
-      <c r="J44" t="n">
+      <c r="J44">
         <v>0.2000514612743399</v>
       </c>
-      <c r="K44" t="n">
+      <c r="K44">
         <v>793</v>
       </c>
-      <c r="L44" t="n">
+      <c r="L44">
         <v>0.0304853966220126</v>
       </c>
-      <c r="M44" t="n">
+      <c r="M44">
         <v>0.0377933740758311</v>
       </c>
-      <c r="N44" t="n">
+      <c r="N44">
         <v>793</v>
       </c>
-      <c r="O44" t="n">
+      <c r="O44">
         <v>0.0458394765804665</v>
       </c>
-      <c r="P44" t="n">
+      <c r="P44">
         <v>0.0580437544601522</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="Q44">
         <v>793</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
+    <row r="45" spans="1:17">
+      <c r="A45" t="s">
+        <v>60</v>
+      </c>
+      <c r="B45">
         <v>3146.503666666667</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45">
         <v>427.134399999999</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45">
         <v>98.802125</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45">
         <v>291.2345352172852</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45">
         <v>0.1070875001968088</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G45">
         <v>0.117699247965641</v>
       </c>
-      <c r="H45" t="n">
+      <c r="H45">
         <v>779</v>
       </c>
-      <c r="I45" t="n">
+      <c r="I45">
         <v>0.155196195873543</v>
       </c>
-      <c r="J45" t="n">
+      <c r="J45">
         <v>0.198925710761768</v>
       </c>
-      <c r="K45" t="n">
+      <c r="K45">
         <v>779</v>
       </c>
-      <c r="L45" t="n">
+      <c r="L45">
         <v>0.0416765277419769</v>
       </c>
-      <c r="M45" t="n">
+      <c r="M45">
         <v>0.0548347279682093</v>
       </c>
-      <c r="N45" t="n">
+      <c r="N45">
         <v>779</v>
       </c>
-      <c r="O45" t="n">
+      <c r="O45">
         <v>0.0427695941911424</v>
       </c>
-      <c r="P45" t="n">
+      <c r="P45">
         <v>0.053071133242001</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="Q45">
         <v>779</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
+    <row r="46" spans="1:17">
+      <c r="A46" t="s">
+        <v>61</v>
+      </c>
+      <c r="B46">
         <v>1589.474666666667</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46">
         <v>66.01693000000159</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46">
         <v>191.1175940000003</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46">
         <v>291.2185363769531</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46">
         <v>0.0715280501743069</v>
       </c>
-      <c r="G46" t="n">
+      <c r="G46">
         <v>0.094638755603713</v>
       </c>
-      <c r="H46" t="n">
+      <c r="H46">
         <v>779</v>
       </c>
-      <c r="I46" t="n">
+      <c r="I46">
         <v>0.095826015268896</v>
       </c>
-      <c r="J46" t="n">
+      <c r="J46">
         <v>0.1266028734055315</v>
       </c>
-      <c r="K46" t="n">
+      <c r="K46">
         <v>779</v>
       </c>
-      <c r="L46" t="n">
+      <c r="L46">
         <v>0.104905599563068</v>
       </c>
-      <c r="M46" t="n">
+      <c r="M46">
         <v>0.1413334277945302</v>
       </c>
-      <c r="N46" t="n">
+      <c r="N46">
         <v>779</v>
       </c>
-      <c r="O46" t="n">
+      <c r="O46">
         <v>0.0952904136502952</v>
       </c>
-      <c r="P46" t="n">
+      <c r="P46">
         <v>0.1259251188056528</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="Q46">
         <v>779</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
+    <row r="47" spans="1:17">
+      <c r="A47" t="s">
+        <v>62</v>
+      </c>
+      <c r="B47">
         <v>413.5030000000013</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47">
         <v>0.2110080000002199</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47">
         <v>81.02352999999948</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47">
         <v>290.4831008911133</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47">
         <v>0.0358354520504641</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G47">
         <v>0.0553174601539634</v>
       </c>
-      <c r="H47" t="n">
+      <c r="H47">
         <v>779</v>
       </c>
-      <c r="I47" t="n">
+      <c r="I47">
         <v>0.08480570714394089</v>
       </c>
-      <c r="J47" t="n">
+      <c r="J47">
         <v>0.1204445756646529</v>
       </c>
-      <c r="K47" t="n">
+      <c r="K47">
         <v>779</v>
       </c>
-      <c r="L47" t="n">
+      <c r="L47">
         <v>0.0646197650103722</v>
       </c>
-      <c r="M47" t="n">
+      <c r="M47">
         <v>0.0775475638738263</v>
       </c>
-      <c r="N47" t="n">
+      <c r="N47">
         <v>779</v>
       </c>
-      <c r="O47" t="n">
+      <c r="O47">
         <v>0.0775758661897432</v>
       </c>
-      <c r="P47" t="n">
+      <c r="P47">
         <v>0.091745878994345</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="Q47">
         <v>779</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
+    <row r="48" spans="1:17">
+      <c r="A48" t="s">
+        <v>63</v>
+      </c>
+      <c r="B48">
         <v>1393.780000000001</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48">
         <v>153.04241</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48">
         <v>162.047309999999</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48">
         <v>289.0143966674805</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48">
         <v>0.1231124587477155</v>
       </c>
-      <c r="G48" t="n">
+      <c r="G48">
         <v>0.1557160751998217</v>
       </c>
-      <c r="H48" t="n">
+      <c r="H48">
         <v>765</v>
       </c>
-      <c r="I48" t="n">
+      <c r="I48">
         <v>0.0842367987006928</v>
       </c>
-      <c r="J48" t="n">
+      <c r="J48">
         <v>0.1115213910115858</v>
       </c>
-      <c r="K48" t="n">
+      <c r="K48">
         <v>765</v>
       </c>
-      <c r="L48" t="n">
+      <c r="L48">
         <v>0.0726059037237516</v>
       </c>
-      <c r="M48" t="n">
+      <c r="M48">
         <v>0.0985603580318196</v>
       </c>
-      <c r="N48" t="n">
+      <c r="N48">
         <v>765</v>
       </c>
-      <c r="O48" t="n">
+      <c r="O48">
         <v>0.0706125507029411</v>
       </c>
-      <c r="P48" t="n">
+      <c r="P48">
         <v>0.0913771972531133</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="Q48">
         <v>765</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
+    <row r="49" spans="1:17">
+      <c r="A49" t="s">
+        <v>64</v>
+      </c>
+      <c r="B49">
         <v>1882.030333333335</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49">
         <v>30.35407314999981</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49">
         <v>177.6663759999988</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49">
         <v>287.2538795471191</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49">
         <v>0.0801551487845259</v>
       </c>
-      <c r="G49" t="n">
+      <c r="G49">
         <v>0.1189595130016079</v>
       </c>
-      <c r="H49" t="n">
+      <c r="H49">
         <v>728</v>
       </c>
-      <c r="I49" t="n">
+      <c r="I49">
         <v>0.0787741244842651</v>
       </c>
-      <c r="J49" t="n">
+      <c r="J49">
         <v>0.1100776138082259</v>
       </c>
-      <c r="K49" t="n">
+      <c r="K49">
         <v>728</v>
       </c>
-      <c r="L49" t="n">
+      <c r="L49">
         <v>0.07836419703206041</v>
       </c>
-      <c r="M49" t="n">
+      <c r="M49">
         <v>0.1106441437662516</v>
       </c>
-      <c r="N49" t="n">
+      <c r="N49">
         <v>728</v>
       </c>
-      <c r="O49" t="n">
+      <c r="O49">
         <v>0.078772102326717</v>
       </c>
-      <c r="P49" t="n">
+      <c r="P49">
         <v>0.1022545130812279</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="Q49">
         <v>728</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
+    <row r="50" spans="1:17">
+      <c r="A50" t="s">
+        <v>65</v>
+      </c>
+      <c r="B50">
         <v>2399.711333333334</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50">
         <v>240.7910229999998</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50">
         <v>158.49615</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50">
         <v>286.9596214294434</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50">
         <v>0.0928267004484237</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G50">
         <v>0.1192706469671933</v>
       </c>
-      <c r="H50" t="n">
+      <c r="H50">
         <v>710</v>
       </c>
-      <c r="I50" t="n">
+      <c r="I50">
         <v>0.109600689433845</v>
       </c>
-      <c r="J50" t="n">
+      <c r="J50">
         <v>0.1444972330052158</v>
       </c>
-      <c r="K50" t="n">
+      <c r="K50">
         <v>710</v>
       </c>
-      <c r="L50" t="n">
+      <c r="L50">
         <v>0.0785510485375493</v>
       </c>
-      <c r="M50" t="n">
+      <c r="M50">
         <v>0.1039258613584512</v>
       </c>
-      <c r="N50" t="n">
+      <c r="N50">
         <v>710</v>
       </c>
-      <c r="O50" t="n">
+      <c r="O50">
         <v>0.07541806581883941</v>
       </c>
-      <c r="P50" t="n">
+      <c r="P50">
         <v>0.09691540166416319</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="Q50">
         <v>710</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
+    <row r="51" spans="1:17">
+      <c r="A51" t="s">
+        <v>66</v>
+      </c>
+      <c r="B51">
         <v>3332.377000000001</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51">
         <v>349.8184000000001</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51">
         <v>108.6764429999996</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51">
         <v>288.116153717041</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51">
         <v>0.0994796540758513</v>
       </c>
-      <c r="G51" t="n">
+      <c r="G51">
         <v>0.1099572884462835</v>
       </c>
-      <c r="H51" t="n">
+      <c r="H51">
         <v>748</v>
       </c>
-      <c r="I51" t="n">
+      <c r="I51">
         <v>0.1466390307508288</v>
       </c>
-      <c r="J51" t="n">
+      <c r="J51">
         <v>0.189427689382791</v>
       </c>
-      <c r="K51" t="n">
+      <c r="K51">
         <v>748</v>
       </c>
-      <c r="L51" t="n">
+      <c r="L51">
         <v>0.0411355662621657</v>
       </c>
-      <c r="M51" t="n">
+      <c r="M51">
         <v>0.0525971443726514</v>
       </c>
-      <c r="N51" t="n">
+      <c r="N51">
         <v>748</v>
       </c>
-      <c r="O51" t="n">
+      <c r="O51">
         <v>0.0465751948943716</v>
       </c>
-      <c r="P51" t="n">
+      <c r="P51">
         <v>0.0585910281870529</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="Q51">
         <v>748</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
+    <row r="52" spans="1:17">
+      <c r="A52" t="s">
+        <v>67</v>
+      </c>
+      <c r="B52">
         <v>2956.7875</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52">
         <v>359.2070000000001</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52">
         <v>110.1772779999992</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52">
         <v>291.0145568847656</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F52">
         <v>0.1049952648800578</v>
       </c>
-      <c r="G52" t="n">
+      <c r="G52">
         <v>0.1199973547568974</v>
       </c>
-      <c r="H52" t="n">
+      <c r="H52">
         <v>765</v>
       </c>
-      <c r="I52" t="n">
+      <c r="I52">
         <v>0.1446642510520261</v>
       </c>
-      <c r="J52" t="n">
+      <c r="J52">
         <v>0.1863542921309741</v>
       </c>
-      <c r="K52" t="n">
+      <c r="K52">
         <v>765</v>
       </c>
-      <c r="L52" t="n">
+      <c r="L52">
         <v>0.0413789903767058</v>
       </c>
-      <c r="M52" t="n">
+      <c r="M52">
         <v>0.0534975539334112</v>
       </c>
-      <c r="N52" t="n">
+      <c r="N52">
         <v>765</v>
       </c>
-      <c r="O52" t="n">
+      <c r="O52">
         <v>0.0445623431495163</v>
       </c>
-      <c r="P52" t="n">
+      <c r="P52">
         <v>0.0573863447849358</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="Q52">
         <v>765</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
+    <row r="53" spans="1:17">
+      <c r="A53" t="s">
+        <v>68</v>
+      </c>
+      <c r="B53">
         <v>1431.021333333334</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53">
         <v>115.9725600000002</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53">
         <v>176.927044</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53">
         <v>291.644302368164</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F53">
         <v>0.0854545435523672</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G53">
         <v>0.1198279583218318</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H53">
         <v>765</v>
       </c>
-      <c r="I53" t="n">
+      <c r="I53">
         <v>0.0800945709622562</v>
       </c>
-      <c r="J53" t="n">
+      <c r="J53">
         <v>0.1016467528899911</v>
       </c>
-      <c r="K53" t="n">
+      <c r="K53">
         <v>765</v>
       </c>
-      <c r="L53" t="n">
+      <c r="L53">
         <v>0.06696723972192151</v>
       </c>
-      <c r="M53" t="n">
+      <c r="M53">
         <v>0.08313368931055121</v>
       </c>
-      <c r="N53" t="n">
+      <c r="N53">
         <v>765</v>
       </c>
-      <c r="O53" t="n">
+      <c r="O53">
         <v>0.0834491200204836</v>
       </c>
-      <c r="P53" t="n">
+      <c r="P53">
         <v>0.1028483971229249</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="Q53">
         <v>765</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
+    <row r="54" spans="1:17">
+      <c r="A54" t="s">
+        <v>69</v>
+      </c>
+      <c r="B54">
         <v>859.7560000000004</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54">
         <v>0.5546670000001086</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54">
         <v>98.77573959999997</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54">
         <v>291.3192443847656</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F54">
         <v>0.0462390606504386</v>
       </c>
-      <c r="G54" t="n">
+      <c r="G54">
         <v>0.0685012923717145</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H54">
         <v>765</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I54">
         <v>0.0725418039413987</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J54">
         <v>0.110813639954058</v>
       </c>
-      <c r="K54" t="n">
+      <c r="K54">
         <v>765</v>
       </c>
-      <c r="L54" t="n">
+      <c r="L54">
         <v>0.08199940564807839</v>
       </c>
-      <c r="M54" t="n">
+      <c r="M54">
         <v>0.1128487431212585</v>
       </c>
-      <c r="N54" t="n">
+      <c r="N54">
         <v>765</v>
       </c>
-      <c r="O54" t="n">
+      <c r="O54">
         <v>0.0600406712196601</v>
       </c>
-      <c r="P54" t="n">
+      <c r="P54">
         <v>0.08065847903407999</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="Q54">
         <v>765</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
+    <row r="55" spans="1:17">
+      <c r="A55" t="s">
+        <v>70</v>
+      </c>
+      <c r="B55">
         <v>1389.355000000001</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C55">
         <v>17.45573750000003</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55">
         <v>156.5320825</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55">
         <v>288.5981750488281</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F55">
         <v>0.07933886174353499</v>
       </c>
-      <c r="G55" t="n">
+      <c r="G55">
         <v>0.1140444066816095</v>
       </c>
-      <c r="H55" t="n">
+      <c r="H55">
         <v>756</v>
       </c>
-      <c r="I55" t="n">
+      <c r="I55">
         <v>0.0813140562506732</v>
       </c>
-      <c r="J55" t="n">
+      <c r="J55">
         <v>0.1111680649850498</v>
       </c>
-      <c r="K55" t="n">
+      <c r="K55">
         <v>756</v>
       </c>
-      <c r="L55" t="n">
+      <c r="L55">
         <v>0.0721031603250529</v>
       </c>
-      <c r="M55" t="n">
+      <c r="M55">
         <v>0.0961418190156427</v>
       </c>
-      <c r="N55" t="n">
+      <c r="N55">
         <v>756</v>
       </c>
-      <c r="O55" t="n">
+      <c r="O55">
         <v>0.09414761726649459</v>
       </c>
-      <c r="P55" t="n">
+      <c r="P55">
         <v>0.1306718498193301</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="Q55">
         <v>756</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
+    <row r="56" spans="1:17">
+      <c r="A56" t="s">
+        <v>71</v>
+      </c>
+      <c r="B56">
         <v>1369.743666666667</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C56">
         <v>52.54296899999997</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56">
         <v>151.0425170000001</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56">
         <v>288.1994018554688</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56">
         <v>0.0964390703099576</v>
       </c>
-      <c r="G56" t="n">
+      <c r="G56">
         <v>0.1305255722795973</v>
       </c>
-      <c r="H56" t="n">
+      <c r="H56">
         <v>737</v>
       </c>
-      <c r="I56" t="n">
+      <c r="I56">
         <v>0.1053000842914789</v>
       </c>
-      <c r="J56" t="n">
+      <c r="J56">
         <v>0.1396133621124882</v>
       </c>
-      <c r="K56" t="n">
+      <c r="K56">
         <v>737</v>
       </c>
-      <c r="L56" t="n">
+      <c r="L56">
         <v>0.0879400652763907</v>
       </c>
-      <c r="M56" t="n">
+      <c r="M56">
         <v>0.1105018297807736</v>
       </c>
-      <c r="N56" t="n">
+      <c r="N56">
         <v>737</v>
       </c>
-      <c r="O56" t="n">
+      <c r="O56">
         <v>0.0819697298450746</v>
       </c>
-      <c r="P56" t="n">
+      <c r="P56">
         <v>0.1127538001866255</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="Q56">
         <v>737</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
+    <row r="57" spans="1:17">
+      <c r="A57" t="s">
+        <v>72</v>
+      </c>
+      <c r="B57">
         <v>2168.093333333333</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C57">
         <v>309.16779</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57">
         <v>107.2448449999993</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57">
         <v>288.5802612304688</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57">
         <v>0.128981116361595</v>
       </c>
-      <c r="G57" t="n">
+      <c r="G57">
         <v>0.1577217822157139</v>
       </c>
-      <c r="H57" t="n">
+      <c r="H57">
         <v>737</v>
       </c>
-      <c r="I57" t="n">
+      <c r="I57">
         <v>0.1283891854325644</v>
       </c>
-      <c r="J57" t="n">
+      <c r="J57">
         <v>0.1727254982477503</v>
       </c>
-      <c r="K57" t="n">
+      <c r="K57">
         <v>737</v>
       </c>
-      <c r="L57" t="n">
+      <c r="L57">
         <v>0.0659226996030122</v>
       </c>
-      <c r="M57" t="n">
+      <c r="M57">
         <v>0.0972059275262319</v>
       </c>
-      <c r="N57" t="n">
+      <c r="N57">
         <v>737</v>
       </c>
-      <c r="O57" t="n">
+      <c r="O57">
         <v>0.0684713241486431</v>
       </c>
-      <c r="P57" t="n">
+      <c r="P57">
         <v>0.08859711192317329</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="Q57">
         <v>737</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
+    <row r="58" spans="1:17">
+      <c r="A58" t="s">
+        <v>73</v>
+      </c>
+      <c r="B58">
         <v>1278.022333333333</v>
       </c>
-      <c r="C58" t="n">
+      <c r="C58">
         <v>42.90233999999873</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58">
         <v>134.9373500000002</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58">
         <v>288.8725891113281</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58">
         <v>0.0677693772581158</v>
       </c>
-      <c r="G58" t="n">
+      <c r="G58">
         <v>0.0968579605871422</v>
       </c>
-      <c r="H58" t="n">
+      <c r="H58">
         <v>737</v>
       </c>
-      <c r="I58" t="n">
+      <c r="I58">
         <v>0.06914517650127</v>
       </c>
-      <c r="J58" t="n">
+      <c r="J58">
         <v>0.10091146190528</v>
       </c>
-      <c r="K58" t="n">
+      <c r="K58">
         <v>737</v>
       </c>
-      <c r="L58" t="n">
+      <c r="L58">
         <v>0.0863221417865129</v>
       </c>
-      <c r="M58" t="n">
+      <c r="M58">
         <v>0.1031374367277146</v>
       </c>
-      <c r="N58" t="n">
+      <c r="N58">
         <v>737</v>
       </c>
-      <c r="O58" t="n">
+      <c r="O58">
         <v>0.07938029239029851</v>
       </c>
-      <c r="P58" t="n">
+      <c r="P58">
         <v>0.09924551344998229</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="Q58">
         <v>737</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
+    <row r="59" spans="1:17">
+      <c r="A59" t="s">
+        <v>74</v>
+      </c>
+      <c r="B59">
         <v>1300.897666666667</v>
       </c>
-      <c r="C59" t="n">
+      <c r="C59">
         <v>11.828125</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59">
         <v>135.4516600000001</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59">
         <v>288.5741729736328</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59">
         <v>0.066846492123718</v>
       </c>
-      <c r="G59" t="n">
+      <c r="G59">
         <v>0.09738036147258471</v>
       </c>
-      <c r="H59" t="n">
+      <c r="H59">
         <v>737</v>
       </c>
-      <c r="I59" t="n">
+      <c r="I59">
         <v>0.09991844163763899</v>
       </c>
-      <c r="J59" t="n">
+      <c r="J59">
         <v>0.1339074326301561</v>
       </c>
-      <c r="K59" t="n">
+      <c r="K59">
         <v>737</v>
       </c>
-      <c r="L59" t="n">
+      <c r="L59">
         <v>0.0735164083690366</v>
       </c>
-      <c r="M59" t="n">
+      <c r="M59">
         <v>0.0942450399475528</v>
       </c>
-      <c r="N59" t="n">
+      <c r="N59">
         <v>737</v>
       </c>
-      <c r="O59" t="n">
+      <c r="O59">
         <v>0.0567528413761736</v>
       </c>
-      <c r="P59" t="n">
+      <c r="P59">
         <v>0.076942297142937</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="Q59">
         <v>737</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2025-09-03</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
+    <row r="60" spans="1:17">
+      <c r="A60" t="s">
+        <v>75</v>
+      </c>
+      <c r="B60">
         <v>2648.538</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C60">
         <v>147.945748000001</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60">
         <v>166.0821955000002</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60">
         <v>288.8448143005371</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60">
         <v>0.0729408476237498</v>
       </c>
-      <c r="G60" t="n">
+      <c r="G60">
         <v>0.0916611911350152</v>
       </c>
-      <c r="H60" t="n">
+      <c r="H60">
         <v>684</v>
       </c>
-      <c r="I60" t="n">
+      <c r="I60">
         <v>0.0992255844560672</v>
       </c>
-      <c r="J60" t="n">
+      <c r="J60">
         <v>0.1230147215424178</v>
       </c>
-      <c r="K60" t="n">
+      <c r="K60">
         <v>684</v>
       </c>
-      <c r="L60" t="n">
+      <c r="L60">
         <v>0.0711409092045321</v>
       </c>
-      <c r="M60" t="n">
+      <c r="M60">
         <v>0.0868505063110714</v>
       </c>
-      <c r="N60" t="n">
+      <c r="N60">
         <v>684</v>
       </c>
-      <c r="O60" t="n">
+      <c r="O60">
         <v>0.07271930550599121</v>
       </c>
-      <c r="P60" t="n">
+      <c r="P60">
         <v>0.0897566983052782</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="Q60">
         <v>684</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
+    <row r="61" spans="1:17">
+      <c r="A61" t="s">
+        <v>76</v>
+      </c>
+      <c r="B61">
         <v>2295.245333333334</v>
       </c>
-      <c r="C61" t="n">
+      <c r="C61">
         <v>145.8134730000006</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61">
         <v>175.9685179999988</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61">
         <v>290.2287673950195</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F61">
         <v>0.0884220739475014</v>
       </c>
-      <c r="G61" t="n">
+      <c r="G61">
         <v>0.1111140625540413</v>
       </c>
-      <c r="H61" t="n">
+      <c r="H61">
         <v>564</v>
       </c>
-      <c r="I61" t="n">
+      <c r="I61">
         <v>0.08980941675468079</v>
       </c>
-      <c r="J61" t="n">
+      <c r="J61">
         <v>0.1259844408914762</v>
       </c>
-      <c r="K61" t="n">
+      <c r="K61">
         <v>564</v>
       </c>
-      <c r="L61" t="n">
+      <c r="L61">
         <v>0.057593804303425</v>
       </c>
-      <c r="M61" t="n">
+      <c r="M61">
         <v>0.06986251301644721</v>
       </c>
-      <c r="N61" t="n">
+      <c r="N61">
         <v>564</v>
       </c>
-      <c r="O61" t="n">
+      <c r="O61">
         <v>0.0576195679640957</v>
       </c>
-      <c r="P61" t="n">
+      <c r="P61">
         <v>0.0718768990953397</v>
       </c>
-      <c r="Q61" t="n">
+      <c r="Q61">
         <v>564</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
+    <row r="62" spans="1:17">
+      <c r="A62" t="s">
+        <v>77</v>
+      </c>
+      <c r="B62">
         <v>764.4350000000003</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C62">
         <v>2.785153600000001</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62">
         <v>118.35258</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62">
         <v>287.8764953613281</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62">
         <v>0.0662852262966821</v>
       </c>
-      <c r="G62" t="n">
+      <c r="G62">
         <v>0.0971636328710089</v>
       </c>
-      <c r="H62" t="n">
+      <c r="H62">
         <v>525</v>
       </c>
-      <c r="I62" t="n">
+      <c r="I62">
         <v>0.0796759152064381</v>
       </c>
-      <c r="J62" t="n">
+      <c r="J62">
         <v>0.1069966193839738</v>
       </c>
-      <c r="K62" t="n">
+      <c r="K62">
         <v>525</v>
       </c>
-      <c r="L62" t="n">
+      <c r="L62">
         <v>0.07299939815535229</v>
       </c>
-      <c r="M62" t="n">
+      <c r="M62">
         <v>0.0911314069342801</v>
       </c>
-      <c r="N62" t="n">
+      <c r="N62">
         <v>525</v>
       </c>
-      <c r="O62" t="n">
+      <c r="O62">
         <v>0.068688444290019</v>
       </c>
-      <c r="P62" t="n">
+      <c r="P62">
         <v>0.0876237732839545</v>
       </c>
-      <c r="Q62" t="n">
+      <c r="Q62">
         <v>525</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
+    <row r="63" spans="1:17">
+      <c r="A63" t="s">
+        <v>78</v>
+      </c>
+      <c r="B63">
         <v>2790.479000000001</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C63">
         <v>219.3150509999996</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63">
         <v>148.71047</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63">
         <v>284.9880256652832</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F63">
         <v>0.0944610924510374</v>
       </c>
-      <c r="G63" t="n">
+      <c r="G63">
         <v>0.1197750431107939</v>
       </c>
-      <c r="H63" t="n">
+      <c r="H63">
         <v>636</v>
       </c>
-      <c r="I63" t="n">
+      <c r="I63">
         <v>0.1003785236783805</v>
       </c>
-      <c r="J63" t="n">
+      <c r="J63">
         <v>0.1283418122768323</v>
       </c>
-      <c r="K63" t="n">
+      <c r="K63">
         <v>636</v>
       </c>
-      <c r="L63" t="n">
+      <c r="L63">
         <v>0.0470488646808018</v>
       </c>
-      <c r="M63" t="n">
+      <c r="M63">
         <v>0.0616820548389437</v>
       </c>
-      <c r="N63" t="n">
+      <c r="N63">
         <v>636</v>
       </c>
-      <c r="O63" t="n">
+      <c r="O63">
         <v>0.0680787037184119</v>
       </c>
-      <c r="P63" t="n">
+      <c r="P63">
         <v>0.09140726419196669</v>
       </c>
-      <c r="Q63" t="n">
+      <c r="Q63">
         <v>636</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
+    <row r="64" spans="1:17">
+      <c r="A64" t="s">
+        <v>79</v>
+      </c>
+      <c r="B64">
         <v>3001.487333333334</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C64">
         <v>160.0816999999997</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64">
         <v>189.9616100000002</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64">
         <v>286.3816146850586</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F64">
         <v>0.06930337281771259</v>
       </c>
-      <c r="G64" t="n">
+      <c r="G64">
         <v>0.08981739825076759</v>
       </c>
-      <c r="H64" t="n">
+      <c r="H64">
         <v>724</v>
       </c>
-      <c r="I64" t="n">
+      <c r="I64">
         <v>0.08704527909463119</v>
       </c>
-      <c r="J64" t="n">
+      <c r="J64">
         <v>0.1124227260804634</v>
       </c>
-      <c r="K64" t="n">
+      <c r="K64">
         <v>724</v>
       </c>
-      <c r="L64" t="n">
+      <c r="L64">
         <v>0.0479918759660911</v>
       </c>
-      <c r="M64" t="n">
+      <c r="M64">
         <v>0.0570629873275917</v>
       </c>
-      <c r="N64" t="n">
+      <c r="N64">
         <v>724</v>
       </c>
-      <c r="O64" t="n">
+      <c r="O64">
         <v>0.0793663382133977</v>
       </c>
-      <c r="P64" t="n">
+      <c r="P64">
         <v>0.0933469802205454</v>
       </c>
-      <c r="Q64" t="n">
+      <c r="Q64">
         <v>724</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
+    <row r="65" spans="1:17">
+      <c r="A65" t="s">
+        <v>80</v>
+      </c>
+      <c r="B65">
         <v>1132.651</v>
       </c>
-      <c r="C65" t="n">
+      <c r="C65">
         <v>15.85920000000033</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65">
         <v>168.8549900000007</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65">
         <v>288.3441123962402</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F65">
         <v>0.0906060919040889</v>
       </c>
-      <c r="G65" t="n">
+      <c r="G65">
         <v>0.1280061959698507</v>
       </c>
-      <c r="H65" t="n">
+      <c r="H65">
         <v>724</v>
       </c>
-      <c r="I65" t="n">
+      <c r="I65">
         <v>0.0743605954362237</v>
       </c>
-      <c r="J65" t="n">
+      <c r="J65">
         <v>0.1047051086183984</v>
       </c>
-      <c r="K65" t="n">
+      <c r="K65">
         <v>724</v>
       </c>
-      <c r="L65" t="n">
+      <c r="L65">
         <v>0.07176737650323201</v>
       </c>
-      <c r="M65" t="n">
+      <c r="M65">
         <v>0.0869254150501165</v>
       </c>
-      <c r="N65" t="n">
+      <c r="N65">
         <v>724</v>
       </c>
-      <c r="O65" t="n">
+      <c r="O65">
         <v>0.0884126097450138</v>
       </c>
-      <c r="P65" t="n">
+      <c r="P65">
         <v>0.1079060509412507</v>
       </c>
-      <c r="Q65" t="n">
+      <c r="Q65">
         <v>724</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
+    <row r="66" spans="1:17">
+      <c r="A66" t="s">
+        <v>81</v>
+      </c>
+      <c r="B66">
         <v>621.4836666666669</v>
       </c>
-      <c r="C66" t="n">
+      <c r="C66">
         <v>3.208262999999988</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66">
         <v>105.956085</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66">
         <v>288.1806030273438</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F66">
         <v>0.0908454665226421</v>
       </c>
-      <c r="G66" t="n">
+      <c r="G66">
         <v>0.1229556467331714</v>
       </c>
-      <c r="H66" t="n">
+      <c r="H66">
         <v>710</v>
       </c>
-      <c r="I66" t="n">
+      <c r="I66">
         <v>0.09521574170376899</v>
       </c>
-      <c r="J66" t="n">
+      <c r="J66">
         <v>0.1275160971186765</v>
       </c>
-      <c r="K66" t="n">
+      <c r="K66">
         <v>710</v>
       </c>
-      <c r="L66" t="n">
+      <c r="L66">
         <v>0.08884933576821399</v>
       </c>
-      <c r="M66" t="n">
+      <c r="M66">
         <v>0.1137555750158065</v>
       </c>
-      <c r="N66" t="n">
+      <c r="N66">
         <v>710</v>
       </c>
-      <c r="O66" t="n">
+      <c r="O66">
         <v>0.06710710703442251</v>
       </c>
-      <c r="P66" t="n">
+      <c r="P66">
         <v>0.0897061377585627</v>
       </c>
-      <c r="Q66" t="n">
+      <c r="Q66">
         <v>710</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
+    <row r="67" spans="1:17">
+      <c r="A67" t="s">
+        <v>82</v>
+      </c>
+      <c r="B67">
         <v>648.9936666666667</v>
       </c>
-      <c r="C67" t="n">
+      <c r="C67">
         <v>0.3305157499999041</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67">
         <v>105.7214279999993</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67">
         <v>286.2212753295898</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F67">
         <v>0.0463705145109156</v>
       </c>
-      <c r="G67" t="n">
+      <c r="G67">
         <v>0.0688333610712968</v>
       </c>
-      <c r="H67" t="n">
+      <c r="H67">
         <v>710</v>
       </c>
-      <c r="I67" t="n">
+      <c r="I67">
         <v>0.0448412175708971</v>
       </c>
-      <c r="J67" t="n">
+      <c r="J67">
         <v>0.0617029626095779</v>
       </c>
-      <c r="K67" t="n">
+      <c r="K67">
         <v>710</v>
       </c>
-      <c r="L67" t="n">
+      <c r="L67">
         <v>0.0923904340413802</v>
       </c>
-      <c r="M67" t="n">
+      <c r="M67">
         <v>0.1124202588557098</v>
       </c>
-      <c r="N67" t="n">
+      <c r="N67">
         <v>710</v>
       </c>
-      <c r="O67" t="n">
+      <c r="O67">
         <v>0.0451127078042253</v>
       </c>
-      <c r="P67" t="n">
+      <c r="P67">
         <v>0.0564512508607113</v>
       </c>
-      <c r="Q67" t="n">
+      <c r="Q67">
         <v>710</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
+    <row r="68" spans="1:17">
+      <c r="A68" t="s">
+        <v>83</v>
+      </c>
+      <c r="B68">
         <v>1858.219</v>
       </c>
-      <c r="C68" t="n">
+      <c r="C68">
         <v>65.18637100000035</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68">
         <v>146.3193934999995</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68">
         <v>286.2762298583984</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F68">
         <v>0.1056726609056889</v>
       </c>
-      <c r="G68" t="n">
+      <c r="G68">
         <v>0.1421830858776155</v>
       </c>
-      <c r="H68" t="n">
+      <c r="H68">
         <v>710</v>
       </c>
-      <c r="I68" t="n">
+      <c r="I68">
         <v>0.08912262328643659</v>
       </c>
-      <c r="J68" t="n">
+      <c r="J68">
         <v>0.1227517921389738</v>
       </c>
-      <c r="K68" t="n">
+      <c r="K68">
         <v>710</v>
       </c>
-      <c r="L68" t="n">
+      <c r="L68">
         <v>0.0807004296368309</v>
       </c>
-      <c r="M68" t="n">
+      <c r="M68">
         <v>0.1019804933619196</v>
       </c>
-      <c r="N68" t="n">
+      <c r="N68">
         <v>710</v>
       </c>
-      <c r="O68" t="n">
+      <c r="O68">
         <v>0.1050082371459154</v>
       </c>
-      <c r="P68" t="n">
+      <c r="P68">
         <v>0.1372633787847962</v>
       </c>
-      <c r="Q68" t="n">
+      <c r="Q68">
         <v>710</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
+    <row r="69" spans="1:17">
+      <c r="A69" t="s">
+        <v>84</v>
+      </c>
+      <c r="B69">
         <v>1274.619333333333</v>
       </c>
-      <c r="C69" t="n">
+      <c r="C69">
         <v>36.41923469999974</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69">
         <v>143.7036760000001</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69">
         <v>287.2194442749023</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69">
         <v>0.0843911646419799</v>
       </c>
-      <c r="G69" t="n">
+      <c r="G69">
         <v>0.1153453679947191</v>
       </c>
-      <c r="H69" t="n">
+      <c r="H69">
         <v>710</v>
       </c>
-      <c r="I69" t="n">
+      <c r="I69">
         <v>0.0764916291136563</v>
       </c>
-      <c r="J69" t="n">
+      <c r="J69">
         <v>0.1096905405172485</v>
       </c>
-      <c r="K69" t="n">
+      <c r="K69">
         <v>710</v>
       </c>
-      <c r="L69" t="n">
+      <c r="L69">
         <v>0.06576548937169011</v>
       </c>
-      <c r="M69" t="n">
+      <c r="M69">
         <v>0.0824837426066827</v>
       </c>
-      <c r="N69" t="n">
+      <c r="N69">
         <v>710</v>
       </c>
-      <c r="O69" t="n">
+      <c r="O69">
         <v>0.0448520959237183</v>
       </c>
-      <c r="P69" t="n">
+      <c r="P69">
         <v>0.0569441212529766</v>
       </c>
-      <c r="Q69" t="n">
+      <c r="Q69">
         <v>710</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
+    <row r="70" spans="1:17">
+      <c r="A70" t="s">
+        <v>85</v>
+      </c>
+      <c r="B70">
         <v>1949.811333333334</v>
       </c>
-      <c r="C70" t="n">
+      <c r="C70">
         <v>52.87718649999999</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70">
         <v>171.81106</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70">
         <v>286.747802734375</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F70">
         <v>0.06702072927469011</v>
       </c>
-      <c r="G70" t="n">
+      <c r="G70">
         <v>0.09894782910985279</v>
       </c>
-      <c r="H70" t="n">
+      <c r="H70">
         <v>696</v>
       </c>
-      <c r="I70" t="n">
+      <c r="I70">
         <v>0.0822621606344827</v>
       </c>
-      <c r="J70" t="n">
+      <c r="J70">
         <v>0.1077882561777892</v>
       </c>
-      <c r="K70" t="n">
+      <c r="K70">
         <v>696</v>
       </c>
-      <c r="L70" t="n">
+      <c r="L70">
         <v>0.058830419564339</v>
       </c>
-      <c r="M70" t="n">
+      <c r="M70">
         <v>0.075343983902386</v>
       </c>
-      <c r="N70" t="n">
+      <c r="N70">
         <v>696</v>
       </c>
-      <c r="O70" t="n">
+      <c r="O70">
         <v>0.07713930688867809</v>
       </c>
-      <c r="P70" t="n">
+      <c r="P70">
         <v>0.1002888194914928</v>
       </c>
-      <c r="Q70" t="n">
+      <c r="Q70">
         <v>696</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
+    <row r="71" spans="1:17">
+      <c r="A71" t="s">
+        <v>86</v>
+      </c>
+      <c r="B71">
         <v>909.4256666666666</v>
       </c>
-      <c r="C71" t="n">
+      <c r="C71">
         <v>58.4131806999998</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71">
         <v>136.1088849999996</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71">
         <v>288.0056610107422</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F71">
         <v>0.09002985352967841</v>
       </c>
-      <c r="G71" t="n">
+      <c r="G71">
         <v>0.1262594126533523</v>
       </c>
-      <c r="H71" t="n">
+      <c r="H71">
         <v>696</v>
       </c>
-      <c r="I71" t="n">
+      <c r="I71">
         <v>0.0839101789969913</v>
       </c>
-      <c r="J71" t="n">
+      <c r="J71">
         <v>0.1154977637890716</v>
       </c>
-      <c r="K71" t="n">
+      <c r="K71">
         <v>696</v>
       </c>
-      <c r="L71" t="n">
+      <c r="L71">
         <v>0.0816876473914511</v>
       </c>
-      <c r="M71" t="n">
+      <c r="M71">
         <v>0.1028834939019549</v>
       </c>
-      <c r="N71" t="n">
+      <c r="N71">
         <v>696</v>
       </c>
-      <c r="O71" t="n">
+      <c r="O71">
         <v>0.06629388562130741</v>
       </c>
-      <c r="P71" t="n">
+      <c r="P71">
         <v>0.0830278116715126</v>
       </c>
-      <c r="Q71" t="n">
+      <c r="Q71">
         <v>696</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
+    <row r="72" spans="1:17">
+      <c r="A72" t="s">
+        <v>87</v>
+      </c>
+      <c r="B72">
         <v>2484.483833333333</v>
       </c>
-      <c r="C72" t="n">
+      <c r="C72">
         <v>132.550287</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72">
         <v>152.1523115</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72">
         <v>288.670108795166</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72">
         <v>0.08377296651531831</v>
       </c>
-      <c r="G72" t="n">
+      <c r="G72">
         <v>0.105214903594456</v>
       </c>
-      <c r="H72" t="n">
+      <c r="H72">
         <v>696</v>
       </c>
-      <c r="I72" t="n">
+      <c r="I72">
         <v>0.1027888647060876</v>
       </c>
-      <c r="J72" t="n">
+      <c r="J72">
         <v>0.1299013874066192</v>
       </c>
-      <c r="K72" t="n">
+      <c r="K72">
         <v>696</v>
       </c>
-      <c r="L72" t="n">
+      <c r="L72">
         <v>0.0619790952769683</v>
       </c>
-      <c r="M72" t="n">
+      <c r="M72">
         <v>0.0806113524712225</v>
       </c>
-      <c r="N72" t="n">
+      <c r="N72">
         <v>696</v>
       </c>
-      <c r="O72" t="n">
+      <c r="O72">
         <v>0.0724727510907614</v>
       </c>
-      <c r="P72" t="n">
+      <c r="P72">
         <v>0.0911704300533228</v>
       </c>
-      <c r="Q72" t="n">
+      <c r="Q72">
         <v>696</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
+    <row r="73" spans="1:17">
+      <c r="A73" t="s">
+        <v>88</v>
+      </c>
+      <c r="B73">
         <v>2060.513166666666</v>
       </c>
-      <c r="C73" t="n">
+      <c r="C73">
         <v>158.0606629999997</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73">
         <v>160.3492539999999</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73">
         <v>287.8631019592285</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F73">
         <v>0.0962956598257593</v>
       </c>
-      <c r="G73" t="n">
+      <c r="G73">
         <v>0.1190263102786509</v>
       </c>
-      <c r="H73" t="n">
+      <c r="H73">
         <v>696</v>
       </c>
-      <c r="I73" t="n">
+      <c r="I73">
         <v>0.0938414911220976</v>
       </c>
-      <c r="J73" t="n">
+      <c r="J73">
         <v>0.1224217475766794</v>
       </c>
-      <c r="K73" t="n">
+      <c r="K73">
         <v>696</v>
       </c>
-      <c r="L73" t="n">
+      <c r="L73">
         <v>0.0655418586461925</v>
       </c>
-      <c r="M73" t="n">
+      <c r="M73">
         <v>0.0855263072456004</v>
       </c>
-      <c r="N73" t="n">
+      <c r="N73">
         <v>696</v>
       </c>
-      <c r="O73" t="n">
+      <c r="O73">
         <v>0.0742075909672701</v>
       </c>
-      <c r="P73" t="n">
+      <c r="P73">
         <v>0.0985429427061643</v>
       </c>
-      <c r="Q73" t="n">
+      <c r="Q73">
         <v>696</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
+    <row r="74" spans="1:17">
+      <c r="A74" t="s">
+        <v>89</v>
+      </c>
+      <c r="B74">
         <v>1694.27</v>
       </c>
-      <c r="C74" t="n">
+      <c r="C74">
         <v>49.01699699999972</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74">
         <v>155.4586489999997</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74">
         <v>286.7011070251465</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F74">
         <v>0.07603640418266699</v>
       </c>
-      <c r="G74" t="n">
+      <c r="G74">
         <v>0.1002838045005905</v>
       </c>
-      <c r="H74" t="n">
+      <c r="H74">
         <v>696</v>
       </c>
-      <c r="I74" t="n">
+      <c r="I74">
         <v>0.0887437957054224</v>
       </c>
-      <c r="J74" t="n">
+      <c r="J74">
         <v>0.1119105845835646</v>
       </c>
-      <c r="K74" t="n">
+      <c r="K74">
         <v>696</v>
       </c>
-      <c r="L74" t="n">
+      <c r="L74">
         <v>0.0731767474297413</v>
       </c>
-      <c r="M74" t="n">
+      <c r="M74">
         <v>0.09484190786043099</v>
       </c>
-      <c r="N74" t="n">
+      <c r="N74">
         <v>696</v>
       </c>
-      <c r="O74" t="n">
+      <c r="O74">
         <v>0.0686783722471839</v>
       </c>
-      <c r="P74" t="n">
+      <c r="P74">
         <v>0.09342211061381921</v>
       </c>
-      <c r="Q74" t="n">
+      <c r="Q74">
         <v>696</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
+    <row r="75" spans="1:17">
+      <c r="A75" t="s">
+        <v>90</v>
+      </c>
+      <c r="B75">
         <v>2190.8865</v>
       </c>
-      <c r="C75" t="n">
+      <c r="C75">
         <v>317.699215</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75">
         <v>108.4314784999999</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75">
         <v>287.8200187683105</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75">
         <v>0.1124961302383443</v>
       </c>
-      <c r="G75" t="n">
+      <c r="G75">
         <v>0.1348855099262453</v>
       </c>
-      <c r="H75" t="n">
+      <c r="H75">
         <v>696</v>
       </c>
-      <c r="I75" t="n">
+      <c r="I75">
         <v>0.1085535486886117</v>
       </c>
-      <c r="J75" t="n">
+      <c r="J75">
         <v>0.1495372019715213</v>
       </c>
-      <c r="K75" t="n">
+      <c r="K75">
         <v>696</v>
       </c>
-      <c r="L75" t="n">
+      <c r="L75">
         <v>0.0637308955893602</v>
       </c>
-      <c r="M75" t="n">
+      <c r="M75">
         <v>0.07985117646677881</v>
       </c>
-      <c r="N75" t="n">
+      <c r="N75">
         <v>696</v>
       </c>
-      <c r="O75" t="n">
+      <c r="O75">
         <v>0.0498987919126436</v>
       </c>
-      <c r="P75" t="n">
+      <c r="P75">
         <v>0.0600935385475691</v>
       </c>
-      <c r="Q75" t="n">
+      <c r="Q75">
         <v>696</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2025-09-19</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
+    <row r="76" spans="1:17">
+      <c r="A76" t="s">
+        <v>91</v>
+      </c>
+      <c r="B76">
         <v>2122.742666666666</v>
       </c>
-      <c r="C76" t="n">
+      <c r="C76">
         <v>301.7373999999991</v>
       </c>
-      <c r="D76" t="n">
+      <c r="D76">
         <v>114.2582440000001</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E76">
         <v>289.8625793457031</v>
       </c>
-      <c r="F76" t="n">
+      <c r="F76">
         <v>0.107630041933326</v>
       </c>
-      <c r="G76" t="n">
+      <c r="G76">
         <v>0.1326704356918577</v>
       </c>
-      <c r="H76" t="n">
+      <c r="H76">
         <v>696</v>
       </c>
-      <c r="I76" t="n">
+      <c r="I76">
         <v>0.1005814628770402</v>
       </c>
-      <c r="J76" t="n">
+      <c r="J76">
         <v>0.1333605588342739</v>
       </c>
-      <c r="K76" t="n">
+      <c r="K76">
         <v>696</v>
       </c>
-      <c r="L76" t="n">
+      <c r="L76">
         <v>0.0667939707875</v>
       </c>
-      <c r="M76" t="n">
+      <c r="M76">
         <v>0.0837346444805835</v>
       </c>
-      <c r="N76" t="n">
+      <c r="N76">
         <v>696</v>
       </c>
-      <c r="O76" t="n">
+      <c r="O76">
         <v>0.0476795472476293</v>
       </c>
-      <c r="P76" t="n">
+      <c r="P76">
         <v>0.0581507272364127</v>
       </c>
-      <c r="Q76" t="n">
+      <c r="Q76">
         <v>696</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
+    <row r="77" spans="1:17">
+      <c r="A77" t="s">
+        <v>92</v>
+      </c>
+      <c r="B77">
         <v>2277.888666666666</v>
       </c>
-      <c r="C77" t="n">
+      <c r="C77">
         <v>279.977205000001</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D77">
         <v>114.20762</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77">
         <v>290.7761840820312</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F77">
         <v>0.1079039588370884</v>
       </c>
-      <c r="G77" t="n">
+      <c r="G77">
         <v>0.1337191400491662</v>
       </c>
-      <c r="H77" t="n">
+      <c r="H77">
         <v>670</v>
       </c>
-      <c r="I77" t="n">
+      <c r="I77">
         <v>0.1110018384699253</v>
       </c>
-      <c r="J77" t="n">
+      <c r="J77">
         <v>0.1441578157030473</v>
       </c>
-      <c r="K77" t="n">
+      <c r="K77">
         <v>670</v>
       </c>
-      <c r="L77" t="n">
+      <c r="L77">
         <v>0.0705075811068656</v>
       </c>
-      <c r="M77" t="n">
+      <c r="M77">
         <v>0.0895111239178871</v>
       </c>
-      <c r="N77" t="n">
+      <c r="N77">
         <v>670</v>
       </c>
-      <c r="O77" t="n">
+      <c r="O77">
         <v>0.0543606066937313</v>
       </c>
-      <c r="P77" t="n">
+      <c r="P77">
         <v>0.0686876897750785</v>
       </c>
-      <c r="Q77" t="n">
+      <c r="Q77">
         <v>670</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
+    <row r="78" spans="1:17">
+      <c r="A78" t="s">
+        <v>93</v>
+      </c>
+      <c r="B78">
         <v>2330.55875</v>
       </c>
-      <c r="C78" t="n">
+      <c r="C78">
         <v>282.5887549999998</v>
       </c>
-      <c r="D78" t="n">
+      <c r="D78">
         <v>104.5811754999997</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E78">
         <v>289.4609069824219</v>
       </c>
-      <c r="F78" t="n">
+      <c r="F78">
         <v>0.1165105794377539</v>
       </c>
-      <c r="G78" t="n">
+      <c r="G78">
         <v>0.1421268161636805</v>
       </c>
-      <c r="H78" t="n">
+      <c r="H78">
         <v>668</v>
       </c>
-      <c r="I78" t="n">
+      <c r="I78">
         <v>0.1184219236376646</v>
       </c>
-      <c r="J78" t="n">
+      <c r="J78">
         <v>0.1633719377804912</v>
       </c>
-      <c r="K78" t="n">
+      <c r="K78">
         <v>668</v>
       </c>
-      <c r="L78" t="n">
+      <c r="L78">
         <v>0.0711679396812724</v>
       </c>
-      <c r="M78" t="n">
+      <c r="M78">
         <v>0.0904170381670745</v>
       </c>
-      <c r="N78" t="n">
+      <c r="N78">
         <v>668</v>
       </c>
-      <c r="O78" t="n">
+      <c r="O78">
         <v>0.058870767830449</v>
       </c>
-      <c r="P78" t="n">
+      <c r="P78">
         <v>0.0741826634579595</v>
       </c>
-      <c r="Q78" t="n">
+      <c r="Q78">
         <v>668</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
+    <row r="79" spans="1:17">
+      <c r="A79" t="s">
+        <v>94</v>
+      </c>
+      <c r="B79">
         <v>127.0256666666661</v>
       </c>
-      <c r="C79" t="n">
+      <c r="C79">
         <v>0.09957024999994245</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D79">
         <v>37.52822600000013</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E79">
         <v>284.8687286376953</v>
       </c>
-      <c r="F79" t="n">
+      <c r="F79">
         <v>0.0130217899024887</v>
       </c>
-      <c r="G79" t="n">
+      <c r="G79">
         <v>0.0197583763720692</v>
       </c>
-      <c r="H79" t="n">
+      <c r="H79">
         <v>668</v>
       </c>
-      <c r="I79" t="n">
+      <c r="I79">
         <v>0.0473360084743113</v>
       </c>
-      <c r="J79" t="n">
+      <c r="J79">
         <v>0.06612106342027869</v>
       </c>
-      <c r="K79" t="n">
+      <c r="K79">
         <v>668</v>
       </c>
-      <c r="L79" t="n">
+      <c r="L79">
         <v>0.1439965850364521</v>
       </c>
-      <c r="M79" t="n">
+      <c r="M79">
         <v>0.166775906318038</v>
       </c>
-      <c r="N79" t="n">
+      <c r="N79">
         <v>668</v>
       </c>
-      <c r="O79" t="n">
+      <c r="O79">
         <v>0.0701620846430988</v>
       </c>
-      <c r="P79" t="n">
+      <c r="P79">
         <v>0.0844635653064314</v>
       </c>
-      <c r="Q79" t="n">
+      <c r="Q79">
         <v>668</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
+    <row r="80" spans="1:17">
+      <c r="A80" t="s">
+        <v>95</v>
+      </c>
+      <c r="B80">
         <v>401.0616666666662</v>
       </c>
-      <c r="C80" t="n">
+      <c r="C80">
         <v>1.050665624999965</v>
       </c>
-      <c r="D80" t="n">
+      <c r="D80">
         <v>64.71815400000008</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E80">
         <v>284.1797943115234</v>
       </c>
-      <c r="F80" t="n">
+      <c r="F80">
         <v>0.0300858525936915</v>
       </c>
-      <c r="G80" t="n">
+      <c r="G80">
         <v>0.0528487832036339</v>
       </c>
-      <c r="H80" t="n">
+      <c r="H80">
         <v>668</v>
       </c>
-      <c r="I80" t="n">
+      <c r="I80">
         <v>0.0457888327912125</v>
       </c>
-      <c r="J80" t="n">
+      <c r="J80">
         <v>0.07343523162067429</v>
       </c>
-      <c r="K80" t="n">
+      <c r="K80">
         <v>668</v>
       </c>
-      <c r="L80" t="n">
+      <c r="L80">
         <v>0.1244688406607251</v>
       </c>
-      <c r="M80" t="n">
+      <c r="M80">
         <v>0.1451778785554828</v>
       </c>
-      <c r="N80" t="n">
+      <c r="N80">
         <v>668</v>
       </c>
-      <c r="O80" t="n">
+      <c r="O80">
         <v>0.0480734354497305</v>
       </c>
-      <c r="P80" t="n">
+      <c r="P80">
         <v>0.0571030662499643</v>
       </c>
-      <c r="Q80" t="n">
+      <c r="Q80">
         <v>668</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
+    <row r="81" spans="1:17">
+      <c r="A81" t="s">
+        <v>96</v>
+      </c>
+      <c r="B81">
         <v>146.6213333333328</v>
       </c>
-      <c r="C81" t="n">
+      <c r="C81">
         <v>0.10546875</v>
       </c>
-      <c r="D81" t="n">
+      <c r="D81">
         <v>33.03991775000009</v>
       </c>
-      <c r="E81" t="n">
+      <c r="E81">
         <v>283.0427856445312</v>
       </c>
-      <c r="F81" t="n">
+      <c r="F81">
         <v>0.0167944207199773</v>
       </c>
-      <c r="G81" t="n">
+      <c r="G81">
         <v>0.0265695249201624</v>
       </c>
-      <c r="H81" t="n">
+      <c r="H81">
         <v>668</v>
       </c>
-      <c r="I81" t="n">
+      <c r="I81">
         <v>0.0412791551865868</v>
       </c>
-      <c r="J81" t="n">
+      <c r="J81">
         <v>0.0593918259808096</v>
       </c>
-      <c r="K81" t="n">
+      <c r="K81">
         <v>668</v>
       </c>
-      <c r="L81" t="n">
+      <c r="L81">
         <v>0.1497115304446107</v>
       </c>
-      <c r="M81" t="n">
+      <c r="M81">
         <v>0.173532836014526</v>
       </c>
-      <c r="N81" t="n">
+      <c r="N81">
         <v>668</v>
       </c>
-      <c r="O81" t="n">
+      <c r="O81">
         <v>0.0576974135131287</v>
       </c>
-      <c r="P81" t="n">
+      <c r="P81">
         <v>0.06639771102594889</v>
       </c>
-      <c r="Q81" t="n">
+      <c r="Q81">
         <v>668</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
+    <row r="82" spans="1:17">
+      <c r="A82" t="s">
+        <v>97</v>
+      </c>
+      <c r="B82">
         <v>873.5321666666662</v>
       </c>
-      <c r="C82" t="n">
+      <c r="C82">
         <v>37.49218890000003</v>
       </c>
-      <c r="D82" t="n">
+      <c r="D82">
         <v>127.6127259999996</v>
       </c>
-      <c r="E82" t="n">
+      <c r="E82">
         <v>282.7912788391113</v>
       </c>
-      <c r="F82" t="n">
+      <c r="F82">
         <v>0.0791857591544961</v>
       </c>
-      <c r="G82" t="n">
+      <c r="G82">
         <v>0.1111457410888726</v>
       </c>
-      <c r="H82" t="n">
+      <c r="H82">
         <v>668</v>
       </c>
-      <c r="I82" t="n">
+      <c r="I82">
         <v>0.07494430094639221</v>
       </c>
-      <c r="J82" t="n">
+      <c r="J82">
         <v>0.101375157235388</v>
       </c>
-      <c r="K82" t="n">
+      <c r="K82">
         <v>668</v>
       </c>
-      <c r="L82" t="n">
+      <c r="L82">
         <v>0.09521021345357029</v>
       </c>
-      <c r="M82" t="n">
+      <c r="M82">
         <v>0.1193865571400095</v>
       </c>
-      <c r="N82" t="n">
+      <c r="N82">
         <v>668</v>
       </c>
-      <c r="O82" t="n">
+      <c r="O82">
         <v>0.0677396717996107</v>
       </c>
-      <c r="P82" t="n">
+      <c r="P82">
         <v>0.0915227437135312</v>
       </c>
-      <c r="Q82" t="n">
+      <c r="Q82">
         <v>668</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
+    <row r="83" spans="1:17">
+      <c r="A83" t="s">
+        <v>98</v>
+      </c>
+      <c r="B83">
         <v>507.1213333333325</v>
       </c>
-      <c r="C83" t="n">
+      <c r="C83">
         <v>8.765625</v>
       </c>
-      <c r="D83" t="n">
+      <c r="D83">
         <v>102.7359719999999</v>
       </c>
-      <c r="E83" t="n">
+      <c r="E83">
         <v>284.8580169677734</v>
       </c>
-      <c r="F83" t="n">
+      <c r="F83">
         <v>0.0829246513982112</v>
       </c>
-      <c r="G83" t="n">
+      <c r="G83">
         <v>0.12863643130322</v>
       </c>
-      <c r="H83" t="n">
+      <c r="H83">
         <v>668</v>
       </c>
-      <c r="I83" t="n">
+      <c r="I83">
         <v>0.0436145073011197</v>
       </c>
-      <c r="J83" t="n">
+      <c r="J83">
         <v>0.0622057104071938</v>
       </c>
-      <c r="K83" t="n">
+      <c r="K83">
         <v>668</v>
       </c>
-      <c r="L83" t="n">
+      <c r="L83">
         <v>0.1205246179995509</v>
       </c>
-      <c r="M83" t="n">
+      <c r="M83">
         <v>0.1431618596503838</v>
       </c>
-      <c r="N83" t="n">
+      <c r="N83">
         <v>668</v>
       </c>
-      <c r="O83" t="n">
+      <c r="O83">
         <v>0.0451839831323952</v>
       </c>
-      <c r="P83" t="n">
+      <c r="P83">
         <v>0.0565491464695871</v>
       </c>
-      <c r="Q83" t="n">
+      <c r="Q83">
         <v>668</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
+    <row r="84" spans="1:17">
+      <c r="A84" t="s">
+        <v>99</v>
+      </c>
+      <c r="B84">
         <v>695.4769999999995</v>
       </c>
-      <c r="C84" t="n">
+      <c r="C84">
         <v>12.13490650000006</v>
       </c>
-      <c r="D84" t="n">
+      <c r="D84">
         <v>99.66413649999993</v>
       </c>
-      <c r="E84" t="n">
+      <c r="E84">
         <v>285.0689392089844</v>
       </c>
-      <c r="F84" t="n">
+      <c r="F84">
         <v>0.09394326657799951</v>
       </c>
-      <c r="G84" t="n">
+      <c r="G84">
         <v>0.1461057950482697</v>
       </c>
-      <c r="H84" t="n">
+      <c r="H84">
         <v>668</v>
       </c>
-      <c r="I84" t="n">
+      <c r="I84">
         <v>0.0750831767948353</v>
       </c>
-      <c r="J84" t="n">
+      <c r="J84">
         <v>0.1130659195468327</v>
       </c>
-      <c r="K84" t="n">
+      <c r="K84">
         <v>668</v>
       </c>
-      <c r="L84" t="n">
+      <c r="L84">
         <v>0.107149146759491</v>
       </c>
-      <c r="M84" t="n">
+      <c r="M84">
         <v>0.1310100127045724</v>
       </c>
-      <c r="N84" t="n">
+      <c r="N84">
         <v>668</v>
       </c>
-      <c r="O84" t="n">
+      <c r="O84">
         <v>0.07767272689137721</v>
       </c>
-      <c r="P84" t="n">
+      <c r="P84">
         <v>0.1144941421416878</v>
       </c>
-      <c r="Q84" t="n">
+      <c r="Q84">
         <v>668</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
+    <row r="85" spans="1:17">
+      <c r="A85" t="s">
+        <v>100</v>
+      </c>
+      <c r="B85">
         <v>869.221333333333</v>
       </c>
-      <c r="C85" t="n">
+      <c r="C85">
         <v>22.06248900000003</v>
       </c>
-      <c r="D85" t="n">
+      <c r="D85">
         <v>116.2399939999999</v>
       </c>
-      <c r="E85" t="n">
+      <c r="E85">
         <v>285.5012512207031</v>
       </c>
-      <c r="F85" t="n">
+      <c r="F85">
         <v>0.0826092607662153</v>
       </c>
-      <c r="G85" t="n">
+      <c r="G85">
         <v>0.1290580638448493</v>
       </c>
-      <c r="H85" t="n">
+      <c r="H85">
         <v>513</v>
       </c>
-      <c r="I85" t="n">
+      <c r="I85">
         <v>0.0500134703971968</v>
       </c>
-      <c r="J85" t="n">
+      <c r="J85">
         <v>0.0666725961589897</v>
       </c>
-      <c r="K85" t="n">
+      <c r="K85">
         <v>513</v>
       </c>
-      <c r="L85" t="n">
+      <c r="L85">
         <v>0.1049628969144249</v>
       </c>
-      <c r="M85" t="n">
+      <c r="M85">
         <v>0.130611379663894</v>
       </c>
-      <c r="N85" t="n">
+      <c r="N85">
         <v>513</v>
       </c>
-      <c r="O85" t="n">
+      <c r="O85">
         <v>0.0366749832329434</v>
       </c>
-      <c r="P85" t="n">
+      <c r="P85">
         <v>0.0469684720230584</v>
       </c>
-      <c r="Q85" t="n">
+      <c r="Q85">
         <v>513</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
+    <row r="86" spans="1:17">
+      <c r="A86" t="s">
+        <v>101</v>
+      </c>
+      <c r="B86">
         <v>928.2076666666662</v>
       </c>
-      <c r="C86" t="n">
+      <c r="C86">
         <v>44.16802800000005</v>
       </c>
-      <c r="D86" t="n">
+      <c r="D86">
         <v>131.6494459999994</v>
       </c>
-      <c r="E86" t="n">
+      <c r="E86">
         <v>283.3715972900391</v>
       </c>
-      <c r="F86" t="n">
+      <c r="F86">
         <v>0.08428033014213041</v>
       </c>
-      <c r="G86" t="n">
+      <c r="G86">
         <v>0.1171480997866277</v>
       </c>
-      <c r="H86" t="n">
+      <c r="H86">
         <v>513</v>
       </c>
-      <c r="I86" t="n">
+      <c r="I86">
         <v>0.0607518902811052</v>
       </c>
-      <c r="J86" t="n">
+      <c r="J86">
         <v>0.0827950895789335</v>
       </c>
-      <c r="K86" t="n">
+      <c r="K86">
         <v>513</v>
       </c>
-      <c r="L86" t="n">
+      <c r="L86">
         <v>0.0952233823150877</v>
       </c>
-      <c r="M86" t="n">
+      <c r="M86">
         <v>0.1163160678748723</v>
       </c>
-      <c r="N86" t="n">
+      <c r="N86">
         <v>513</v>
       </c>
-      <c r="O86" t="n">
+      <c r="O86">
         <v>0.0729610104679337</v>
       </c>
-      <c r="P86" t="n">
+      <c r="P86">
         <v>0.08921949931507719</v>
       </c>
-      <c r="Q86" t="n">
+      <c r="Q86">
         <v>513</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
+    <row r="87" spans="1:17">
+      <c r="A87" t="s">
+        <v>102</v>
+      </c>
+      <c r="B87">
         <v>479.7366666666661</v>
       </c>
-      <c r="C87" t="n">
+      <c r="C87">
         <v>3.145954499999789</v>
       </c>
-      <c r="D87" t="n">
+      <c r="D87">
         <v>94.07513020000005</v>
       </c>
-      <c r="E87" t="n">
+      <c r="E87">
         <v>283.90185546875</v>
       </c>
-      <c r="F87" t="n">
+      <c r="F87">
         <v>0.0714627992338097</v>
       </c>
-      <c r="G87" t="n">
+      <c r="G87">
         <v>0.1051430341171607</v>
       </c>
-      <c r="H87" t="n">
+      <c r="H87">
         <v>654</v>
       </c>
-      <c r="I87" t="n">
+      <c r="I87">
         <v>0.0647570135236315</v>
       </c>
-      <c r="J87" t="n">
+      <c r="J87">
         <v>0.0858129578292447</v>
       </c>
-      <c r="K87" t="n">
+      <c r="K87">
         <v>654</v>
       </c>
-      <c r="L87" t="n">
+      <c r="L87">
         <v>0.1333547259365596</v>
       </c>
-      <c r="M87" t="n">
+      <c r="M87">
         <v>0.1620494926889265</v>
       </c>
-      <c r="N87" t="n">
+      <c r="N87">
         <v>654</v>
       </c>
-      <c r="O87" t="n">
+      <c r="O87">
         <v>0.0573663580404587</v>
       </c>
-      <c r="P87" t="n">
+      <c r="P87">
         <v>0.07303943505256021</v>
       </c>
-      <c r="Q87" t="n">
+      <c r="Q87">
         <v>654</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
+    <row r="88" spans="1:17">
+      <c r="A88" t="s">
+        <v>103</v>
+      </c>
+      <c r="B88">
         <v>1641.007</v>
       </c>
-      <c r="C88" t="n">
+      <c r="C88">
         <v>196.57034</v>
       </c>
-      <c r="D88" t="n">
+      <c r="D88">
         <v>129.5710094999999</v>
       </c>
-      <c r="E88" t="n">
+      <c r="E88">
         <v>280.9747543334961</v>
       </c>
-      <c r="F88" t="n">
+      <c r="F88">
         <v>0.1100774183918123</v>
       </c>
-      <c r="G88" t="n">
+      <c r="G88">
         <v>0.1433044749469973</v>
       </c>
-      <c r="H88" t="n">
+      <c r="H88">
         <v>640</v>
       </c>
-      <c r="I88" t="n">
+      <c r="I88">
         <v>0.0990652881089546</v>
       </c>
-      <c r="J88" t="n">
+      <c r="J88">
         <v>0.1252758398695614</v>
       </c>
-      <c r="K88" t="n">
+      <c r="K88">
         <v>640</v>
       </c>
-      <c r="L88" t="n">
+      <c r="L88">
         <v>0.1010827338708437</v>
       </c>
-      <c r="M88" t="n">
+      <c r="M88">
         <v>0.1253179964512558</v>
       </c>
-      <c r="N88" t="n">
+      <c r="N88">
         <v>640</v>
       </c>
-      <c r="O88" t="n">
+      <c r="O88">
         <v>0.07216425128124999</v>
       </c>
-      <c r="P88" t="n">
+      <c r="P88">
         <v>0.0910181357686931</v>
       </c>
-      <c r="Q88" t="n">
+      <c r="Q88">
         <v>640</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
+    <row r="89" spans="1:17">
+      <c r="A89" t="s">
+        <v>104</v>
+      </c>
+      <c r="B89">
         <v>1638.010333333333</v>
       </c>
-      <c r="C89" t="n">
+      <c r="C89">
         <v>186.707304999999</v>
       </c>
-      <c r="D89" t="n">
+      <c r="D89">
         <v>122.7305574999996</v>
       </c>
-      <c r="E89" t="n">
+      <c r="E89">
         <v>279.2452087402344</v>
       </c>
-      <c r="F89" t="n">
+      <c r="F89">
         <v>0.1085974526571482</v>
       </c>
-      <c r="G89" t="n">
+      <c r="G89">
         <v>0.1498879906898823</v>
       </c>
-      <c r="H89" t="n">
+      <c r="H89">
         <v>640</v>
       </c>
-      <c r="I89" t="n">
+      <c r="I89">
         <v>0.0945548463539687</v>
       </c>
-      <c r="J89" t="n">
+      <c r="J89">
         <v>0.1277293008181722</v>
       </c>
-      <c r="K89" t="n">
+      <c r="K89">
         <v>640</v>
       </c>
-      <c r="L89" t="n">
+      <c r="L89">
         <v>0.1075885043892812</v>
       </c>
-      <c r="M89" t="n">
+      <c r="M89">
         <v>0.1338467955420265</v>
       </c>
-      <c r="N89" t="n">
+      <c r="N89">
         <v>640</v>
       </c>
-      <c r="O89" t="n">
+      <c r="O89">
         <v>0.0700978644617187</v>
       </c>
-      <c r="P89" t="n">
+      <c r="P89">
         <v>0.0869875693441684</v>
       </c>
-      <c r="Q89" t="n">
+      <c r="Q89">
         <v>640</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
+    <row r="90" spans="1:17">
+      <c r="A90" t="s">
+        <v>105</v>
+      </c>
+      <c r="B90">
         <v>2090.626</v>
       </c>
-      <c r="C90" t="n">
+      <c r="C90">
         <v>281.2074549999998</v>
       </c>
-      <c r="D90" t="n">
+      <c r="D90">
         <v>99.21718749999911</v>
       </c>
-      <c r="E90" t="n">
+      <c r="E90">
         <v>279.7323989868164</v>
       </c>
-      <c r="F90" t="n">
+      <c r="F90">
         <v>0.1134660252233532</v>
       </c>
-      <c r="G90" t="n">
+      <c r="G90">
         <v>0.142962431662318</v>
       </c>
-      <c r="H90" t="n">
+      <c r="H90">
         <v>640</v>
       </c>
-      <c r="I90" t="n">
+      <c r="I90">
         <v>0.1190834380585625</v>
       </c>
-      <c r="J90" t="n">
+      <c r="J90">
         <v>0.1523768172355269</v>
       </c>
-      <c r="K90" t="n">
+      <c r="K90">
         <v>640</v>
       </c>
-      <c r="L90" t="n">
+      <c r="L90">
         <v>0.0967711769367343</v>
       </c>
-      <c r="M90" t="n">
+      <c r="M90">
         <v>0.1198037050230898</v>
       </c>
-      <c r="N90" t="n">
+      <c r="N90">
         <v>640</v>
       </c>
-      <c r="O90" t="n">
+      <c r="O90">
         <v>0.0625141083843125</v>
       </c>
-      <c r="P90" t="n">
+      <c r="P90">
         <v>0.0785310812812524</v>
       </c>
-      <c r="Q90" t="n">
+      <c r="Q90">
         <v>640</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
+    <row r="91" spans="1:17">
+      <c r="A91" t="s">
+        <v>106</v>
+      </c>
+      <c r="B91">
         <v>512.7209999999994</v>
       </c>
-      <c r="C91" t="n">
+      <c r="C91">
         <v>0.7245241000005365</v>
       </c>
-      <c r="D91" t="n">
+      <c r="D91">
         <v>39.06084800000006</v>
       </c>
-      <c r="E91" t="n">
+      <c r="E91">
         <v>282.2157516479492</v>
       </c>
-      <c r="F91" t="n">
+      <c r="F91">
         <v>0.0558092685423662</v>
       </c>
-      <c r="G91" t="n">
+      <c r="G91">
         <v>0.09204960341549211</v>
       </c>
-      <c r="H91" t="n">
+      <c r="H91">
         <v>640</v>
       </c>
-      <c r="I91" t="n">
+      <c r="I91">
         <v>0.09359205966739061</v>
       </c>
-      <c r="J91" t="n">
+      <c r="J91">
         <v>0.1364822664438323</v>
       </c>
-      <c r="K91" t="n">
+      <c r="K91">
         <v>640</v>
       </c>
-      <c r="L91" t="n">
+      <c r="L91">
         <v>0.1199101486414843</v>
       </c>
-      <c r="M91" t="n">
+      <c r="M91">
         <v>0.1465975242172143</v>
       </c>
-      <c r="N91" t="n">
+      <c r="N91">
         <v>640</v>
       </c>
-      <c r="O91" t="n">
+      <c r="O91">
         <v>0.09480179334625</v>
       </c>
-      <c r="P91" t="n">
+      <c r="P91">
         <v>0.1194421489982669</v>
       </c>
-      <c r="Q91" t="n">
+      <c r="Q91">
         <v>640</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
+    <row r="92" spans="1:17">
+      <c r="A92" t="s">
+        <v>107</v>
+      </c>
+      <c r="B92">
         <v>1151.503</v>
       </c>
-      <c r="C92" t="n">
+      <c r="C92">
         <v>26.203125</v>
       </c>
-      <c r="D92" t="n">
+      <c r="D92">
         <v>113.3489070000005</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E92">
         <v>281.9266204833984</v>
       </c>
-      <c r="F92" t="n">
+      <c r="F92">
         <v>0.0741786118341146</v>
       </c>
-      <c r="G92" t="n">
+      <c r="G92">
         <v>0.1058804682859077</v>
       </c>
-      <c r="H92" t="n">
+      <c r="H92">
         <v>581</v>
       </c>
-      <c r="I92" t="n">
+      <c r="I92">
         <v>0.0699709149157315</v>
       </c>
-      <c r="J92" t="n">
+      <c r="J92">
         <v>0.08957411110450229</v>
       </c>
-      <c r="K92" t="n">
+      <c r="K92">
         <v>581</v>
       </c>
-      <c r="L92" t="n">
+      <c r="L92">
         <v>0.107459054906265</v>
       </c>
-      <c r="M92" t="n">
+      <c r="M92">
         <v>0.1283181914546001</v>
       </c>
-      <c r="N92" t="n">
+      <c r="N92">
         <v>581</v>
       </c>
-      <c r="O92" t="n">
+      <c r="O92">
         <v>0.0563848905059552</v>
       </c>
-      <c r="P92" t="n">
+      <c r="P92">
         <v>0.07063367549547429</v>
       </c>
-      <c r="Q92" t="n">
+      <c r="Q92">
         <v>581</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
+    <row r="93" spans="1:17">
+      <c r="A93" t="s">
+        <v>108</v>
+      </c>
+      <c r="B93">
         <v>391.7696666666665</v>
       </c>
-      <c r="C93" t="n">
+      <c r="C93">
         <v>1.3671875</v>
       </c>
-      <c r="D93" t="n">
+      <c r="D93">
         <v>74.31460799999991</v>
       </c>
-      <c r="E93" t="n">
+      <c r="E93">
         <v>282.2968978881836</v>
       </c>
-      <c r="F93" t="n">
+      <c r="F93">
         <v>0.0317926130192621</v>
       </c>
-      <c r="G93" t="n">
+      <c r="G93">
         <v>0.0469379272061031</v>
       </c>
-      <c r="H93" t="n">
+      <c r="H93">
         <v>581</v>
       </c>
-      <c r="I93" t="n">
+      <c r="I93">
         <v>0.0516090355359862</v>
       </c>
-      <c r="J93" t="n">
+      <c r="J93">
         <v>0.09314893039498109</v>
       </c>
-      <c r="K93" t="n">
+      <c r="K93">
         <v>436</v>
       </c>
-      <c r="L93" t="n">
+      <c r="L93">
         <v>0.1157827768297706</v>
       </c>
-      <c r="M93" t="n">
+      <c r="M93">
         <v>0.1354087372775692</v>
       </c>
-      <c r="N93" t="n">
+      <c r="N93">
         <v>436</v>
       </c>
-      <c r="O93" t="n">
+      <c r="O93">
         <v>0.0497229841738073</v>
       </c>
-      <c r="P93" t="n">
+      <c r="P93">
         <v>0.06594791912013</v>
       </c>
-      <c r="Q93" t="n">
+      <c r="Q93">
         <v>436</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
+    <row r="94" spans="1:17">
+      <c r="A94" t="s">
+        <v>109</v>
+      </c>
+      <c r="B94">
         <v>358.4503333333333</v>
       </c>
-      <c r="C94" t="n">
+      <c r="C94">
         <v>0.2968840999999997</v>
       </c>
-      <c r="D94" t="n">
+      <c r="D94">
         <v>31.42484999999988</v>
       </c>
-      <c r="E94" t="n">
+      <c r="E94">
         <v>282.7023544311523</v>
       </c>
-      <c r="F94" t="n">
+      <c r="F94">
         <v>0.0359000148318856</v>
       </c>
-      <c r="G94" t="n">
+      <c r="G94">
         <v>0.0600302211053879</v>
       </c>
-      <c r="H94" t="n">
+      <c r="H94">
         <v>569</v>
       </c>
-      <c r="I94" t="n">
+      <c r="I94">
         <v>0.0284620578534337</v>
       </c>
-      <c r="J94" t="n">
+      <c r="J94">
         <v>0.0395709928692778</v>
       </c>
-      <c r="K94" t="n">
+      <c r="K94">
         <v>166</v>
       </c>
-      <c r="L94" t="n">
+      <c r="L94">
         <v>0.0512129655650602</v>
       </c>
-      <c r="M94" t="n">
+      <c r="M94">
         <v>0.0659121946427723</v>
       </c>
-      <c r="N94" t="n">
+      <c r="N94">
         <v>166</v>
       </c>
-      <c r="O94" t="n">
+      <c r="O94">
         <v>0.0396068277254216</v>
       </c>
-      <c r="P94" t="n">
+      <c r="P94">
         <v>0.0524944768209221</v>
       </c>
-      <c r="Q94" t="n">
+      <c r="Q94">
         <v>166</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>